--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N8">

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G11">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G13">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Naftagas</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G25">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Bor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Metalac GM</t>
         </is>
       </c>
       <c r="G26">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="G27">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Teleoptik</t>
         </is>
       </c>
       <c r="G28">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G12">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G13">

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G29">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="G30">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G31">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G32">

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1978,10 +1978,10 @@
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC10">
         <v>0</v>
@@ -2102,13 +2102,13 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -2141,10 +2141,10 @@
         <v>0</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -2793,10 +2793,10 @@
         <v>0</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC15">
         <v>0</v>
@@ -2917,13 +2917,13 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="Q17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1326,10 +1326,10 @@
         <v>0</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>1.61</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.54</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>4.96</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2304,10 +2304,10 @@
         <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.61</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
-        <v>3.54</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>4.96</v>
+        <v>2.45</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -2467,10 +2467,10 @@
         <v>0</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC20">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>2.58</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,34 +2763,34 @@
         <v>3.48</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AA15">
         <v>1.78</v>
@@ -2799,19 +2799,19 @@
         <v>1.98</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,55 +2926,55 @@
         <v>5.26</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3089,55 +3089,55 @@
         <v>2.68</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,80 +2591,80 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>1.88</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="P14">
-        <v>2.58</v>
+        <v>3.48</v>
       </c>
       <c r="Q14">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="R14">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="S14">
+        <v>1.3</v>
+      </c>
+      <c r="T14">
+        <v>3.26</v>
+      </c>
+      <c r="U14">
+        <v>2.51</v>
+      </c>
+      <c r="V14">
+        <v>1.44</v>
+      </c>
+      <c r="W14">
+        <v>1.11</v>
+      </c>
+      <c r="X14">
+        <v>1.03</v>
+      </c>
+      <c r="Y14">
+        <v>1.18</v>
+      </c>
+      <c r="Z14">
+        <v>3.84</v>
+      </c>
+      <c r="AA14">
+        <v>1.78</v>
+      </c>
+      <c r="AB14">
+        <v>1.98</v>
+      </c>
+      <c r="AC14">
+        <v>2.78</v>
+      </c>
+      <c r="AD14">
+        <v>1.34</v>
+      </c>
+      <c r="AE14">
+        <v>1.09</v>
+      </c>
+      <c r="AF14">
+        <v>1.6</v>
+      </c>
+      <c r="AG14">
+        <v>2.15</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ14">
         <v>1.22</v>
       </c>
-      <c r="T14">
-        <v>3.5</v>
-      </c>
-      <c r="U14">
-        <v>2.2</v>
-      </c>
-      <c r="V14">
-        <v>1.62</v>
-      </c>
-      <c r="W14">
-        <v>1.17</v>
-      </c>
-      <c r="X14">
-        <v>1.01</v>
-      </c>
-      <c r="Y14">
-        <v>1.1</v>
-      </c>
-      <c r="Z14">
-        <v>5.1</v>
-      </c>
-      <c r="AA14">
-        <v>1.43</v>
-      </c>
-      <c r="AB14">
-        <v>2.46</v>
-      </c>
-      <c r="AC14">
-        <v>2.13</v>
-      </c>
-      <c r="AD14">
-        <v>1.61</v>
-      </c>
-      <c r="AE14">
-        <v>1.26</v>
-      </c>
-      <c r="AF14">
-        <v>1.44</v>
-      </c>
-      <c r="AG14">
-        <v>2.7</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ14">
-        <v>1.2</v>
-      </c>
       <c r="AK14">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.88</v>
+        <v>2.25</v>
       </c>
       <c r="O15">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="P15">
-        <v>3.48</v>
+        <v>2.58</v>
       </c>
       <c r="Q15">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R15">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="S15">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T15">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="U15">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="V15">
+        <v>1.62</v>
+      </c>
+      <c r="W15">
+        <v>1.17</v>
+      </c>
+      <c r="X15">
+        <v>1.01</v>
+      </c>
+      <c r="Y15">
+        <v>1.1</v>
+      </c>
+      <c r="Z15">
+        <v>5.1</v>
+      </c>
+      <c r="AA15">
+        <v>1.43</v>
+      </c>
+      <c r="AB15">
+        <v>2.46</v>
+      </c>
+      <c r="AC15">
+        <v>2.13</v>
+      </c>
+      <c r="AD15">
+        <v>1.61</v>
+      </c>
+      <c r="AE15">
+        <v>1.26</v>
+      </c>
+      <c r="AF15">
         <v>1.44</v>
       </c>
-      <c r="W15">
-        <v>1.11</v>
-      </c>
-      <c r="X15">
-        <v>1.03</v>
-      </c>
-      <c r="Y15">
-        <v>1.18</v>
-      </c>
-      <c r="Z15">
-        <v>3.84</v>
-      </c>
-      <c r="AA15">
-        <v>1.78</v>
-      </c>
-      <c r="AB15">
-        <v>1.98</v>
-      </c>
-      <c r="AC15">
-        <v>2.78</v>
-      </c>
-      <c r="AD15">
-        <v>1.34</v>
-      </c>
-      <c r="AE15">
-        <v>1.09</v>
-      </c>
-      <c r="AF15">
-        <v>1.6</v>
-      </c>
       <c r="AG15">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>1.83</v>
+        <v>1.55</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>2.31</v>
       </c>
       <c r="O16">
-        <v>3.94</v>
+        <v>3.2</v>
       </c>
       <c r="P16">
-        <v>5.26</v>
+        <v>2.68</v>
       </c>
       <c r="Q16">
-        <v>2.18</v>
+        <v>2.92</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X16">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>3.98</v>
+        <v>3.58</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AB16">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AC16">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AG16">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>2.38</v>
+        <v>1.5</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.31</v>
+        <v>1.51</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="P17">
-        <v>2.68</v>
+        <v>5.26</v>
       </c>
       <c r="Q17">
-        <v>2.92</v>
+        <v>2.18</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S17">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T17">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.65</v>
+        <v>2.45</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
+        <v>1.12</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
+        <v>1.17</v>
+      </c>
+      <c r="Z17">
+        <v>3.98</v>
+      </c>
+      <c r="AA17">
+        <v>1.67</v>
+      </c>
+      <c r="AB17">
+        <v>2.04</v>
+      </c>
+      <c r="AC17">
+        <v>2.69</v>
+      </c>
+      <c r="AD17">
+        <v>1.36</v>
+      </c>
+      <c r="AE17">
         <v>1.1</v>
       </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
-        <v>1.21</v>
-      </c>
-      <c r="Z17">
-        <v>3.58</v>
-      </c>
-      <c r="AA17">
-        <v>1.75</v>
-      </c>
-      <c r="AB17">
-        <v>1.93</v>
-      </c>
-      <c r="AC17">
-        <v>2.83</v>
-      </c>
-      <c r="AD17">
-        <v>1.38</v>
-      </c>
-      <c r="AE17">
-        <v>1.09</v>
-      </c>
       <c r="AF17">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AK17">
-        <v>1.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         </is>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -5851,13 +5851,13 @@
         </is>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -5890,10 +5890,10 @@
         <v>0</v>
       </c>
       <c r="AA34">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB34">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC34">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>5.27</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4097,10 +4097,10 @@
         <v>0</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB23">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU35"/>
+  <dimension ref="A1:AU28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1296,34 +1296,34 @@
         <v>5.2</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AA6">
         <v>1.55</v>
@@ -1332,19 +1332,19 @@
         <v>2.25</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G7">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N7">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G8">
@@ -1609,68 +1609,68 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,34 +1948,34 @@
         <v>6.4</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA10">
         <v>1.79</v>
@@ -1984,19 +1984,19 @@
         <v>1.98</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2111,34 +2111,34 @@
         <v>2.91</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
         <v>1.97</v>
@@ -2147,19 +2147,19 @@
         <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>4.96</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2437,34 +2437,34 @@
         <v>2.45</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
         <v>2.03</v>
@@ -2473,19 +2473,19 @@
         <v>1.78</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,13 +3406,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -3578,34 +3578,34 @@
         <v>5.4</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA20">
         <v>1.83</v>
@@ -3614,19 +3614,19 @@
         <v>1.85</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4067,34 +4067,34 @@
         <v>5.27</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T23">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U23">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA23">
         <v>2.1</v>
@@ -4103,19 +4103,19 @@
         <v>1.62</v>
       </c>
       <c r="AC23">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG23">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK23">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4221,13 +4221,13 @@
         </is>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Q24">
         <v>0</v>
@@ -4352,12 +4352,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Naftagas</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G25">
@@ -4500,27 +4500,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bor</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Metalac GM</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,13 +4547,13 @@
         </is>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:00</t>
+          <t>2026-09-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4663,27 +4663,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC27">
         <v>0</v>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:00</t>
+          <t>2026-09-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -4826,27 +4826,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Teleoptik</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G28">
@@ -4976,1147 +4976,6 @@
         <v>0</v>
       </c>
       <c r="AU28" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Voždovac</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Napredak</t>
-        </is>
-      </c>
-      <c r="G29">
-        <v>0</v>
-      </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29">
-        <v>0</v>
-      </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29">
-        <v>0</v>
-      </c>
-      <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
-      <c r="O29">
-        <v>0</v>
-      </c>
-      <c r="P29">
-        <v>0</v>
-      </c>
-      <c r="Q29">
-        <v>0</v>
-      </c>
-      <c r="R29">
-        <v>0</v>
-      </c>
-      <c r="S29">
-        <v>0</v>
-      </c>
-      <c r="T29">
-        <v>0</v>
-      </c>
-      <c r="U29">
-        <v>0</v>
-      </c>
-      <c r="V29">
-        <v>0</v>
-      </c>
-      <c r="W29">
-        <v>0</v>
-      </c>
-      <c r="X29">
-        <v>0</v>
-      </c>
-      <c r="Y29">
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <v>0</v>
-      </c>
-      <c r="AA29">
-        <v>0</v>
-      </c>
-      <c r="AB29">
-        <v>0</v>
-      </c>
-      <c r="AC29">
-        <v>0</v>
-      </c>
-      <c r="AD29">
-        <v>0</v>
-      </c>
-      <c r="AE29">
-        <v>0</v>
-      </c>
-      <c r="AF29">
-        <v>0</v>
-      </c>
-      <c r="AG29">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ29">
-        <v>0</v>
-      </c>
-      <c r="AK29">
-        <v>0</v>
-      </c>
-      <c r="AL29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>-1</v>
-      </c>
-      <c r="AN29">
-        <v>-1</v>
-      </c>
-      <c r="AO29">
-        <v>-1</v>
-      </c>
-      <c r="AP29">
-        <v>-1</v>
-      </c>
-      <c r="AQ29">
-        <v>0</v>
-      </c>
-      <c r="AR29">
-        <v>0</v>
-      </c>
-      <c r="AS29">
-        <v>0</v>
-      </c>
-      <c r="AT29">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Loznica</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Spartak Subotica</t>
-        </is>
-      </c>
-      <c r="G30">
-        <v>0</v>
-      </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30">
-        <v>0</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30">
-        <v>0</v>
-      </c>
-      <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
-      <c r="O30">
-        <v>0</v>
-      </c>
-      <c r="P30">
-        <v>0</v>
-      </c>
-      <c r="Q30">
-        <v>0</v>
-      </c>
-      <c r="R30">
-        <v>0</v>
-      </c>
-      <c r="S30">
-        <v>0</v>
-      </c>
-      <c r="T30">
-        <v>0</v>
-      </c>
-      <c r="U30">
-        <v>0</v>
-      </c>
-      <c r="V30">
-        <v>0</v>
-      </c>
-      <c r="W30">
-        <v>0</v>
-      </c>
-      <c r="X30">
-        <v>0</v>
-      </c>
-      <c r="Y30">
-        <v>0</v>
-      </c>
-      <c r="Z30">
-        <v>0</v>
-      </c>
-      <c r="AA30">
-        <v>0</v>
-      </c>
-      <c r="AB30">
-        <v>0</v>
-      </c>
-      <c r="AC30">
-        <v>0</v>
-      </c>
-      <c r="AD30">
-        <v>0</v>
-      </c>
-      <c r="AE30">
-        <v>0</v>
-      </c>
-      <c r="AF30">
-        <v>0</v>
-      </c>
-      <c r="AG30">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ30">
-        <v>0</v>
-      </c>
-      <c r="AK30">
-        <v>0</v>
-      </c>
-      <c r="AL30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>-1</v>
-      </c>
-      <c r="AN30">
-        <v>-1</v>
-      </c>
-      <c r="AO30">
-        <v>-1</v>
-      </c>
-      <c r="AP30">
-        <v>-1</v>
-      </c>
-      <c r="AQ30">
-        <v>0</v>
-      </c>
-      <c r="AR30">
-        <v>0</v>
-      </c>
-      <c r="AS30">
-        <v>0</v>
-      </c>
-      <c r="AT30">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Borac Čačak</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bačka Topola</t>
-        </is>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
-      <c r="O31">
-        <v>0</v>
-      </c>
-      <c r="P31">
-        <v>0</v>
-      </c>
-      <c r="Q31">
-        <v>0</v>
-      </c>
-      <c r="R31">
-        <v>0</v>
-      </c>
-      <c r="S31">
-        <v>0</v>
-      </c>
-      <c r="T31">
-        <v>0</v>
-      </c>
-      <c r="U31">
-        <v>0</v>
-      </c>
-      <c r="V31">
-        <v>0</v>
-      </c>
-      <c r="W31">
-        <v>0</v>
-      </c>
-      <c r="X31">
-        <v>0</v>
-      </c>
-      <c r="Y31">
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <v>0</v>
-      </c>
-      <c r="AA31">
-        <v>0</v>
-      </c>
-      <c r="AB31">
-        <v>0</v>
-      </c>
-      <c r="AC31">
-        <v>0</v>
-      </c>
-      <c r="AD31">
-        <v>0</v>
-      </c>
-      <c r="AE31">
-        <v>0</v>
-      </c>
-      <c r="AF31">
-        <v>0</v>
-      </c>
-      <c r="AG31">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ31">
-        <v>0</v>
-      </c>
-      <c r="AK31">
-        <v>0</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>-1</v>
-      </c>
-      <c r="AN31">
-        <v>-1</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>-1</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026/2027</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Semendrija 1924</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>OFK Vršac</t>
-        </is>
-      </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>0</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>0</v>
-      </c>
-      <c r="Q32">
-        <v>0</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>-1</v>
-      </c>
-      <c r="AN32">
-        <v>-1</v>
-      </c>
-      <c r="AO32">
-        <v>-1</v>
-      </c>
-      <c r="AP32">
-        <v>-1</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Boston Legacy W</t>
-        </is>
-      </c>
-      <c r="G33">
-        <v>0</v>
-      </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
-      <c r="P33">
-        <v>0</v>
-      </c>
-      <c r="Q33">
-        <v>0</v>
-      </c>
-      <c r="R33">
-        <v>0</v>
-      </c>
-      <c r="S33">
-        <v>0</v>
-      </c>
-      <c r="T33">
-        <v>0</v>
-      </c>
-      <c r="U33">
-        <v>0</v>
-      </c>
-      <c r="V33">
-        <v>0</v>
-      </c>
-      <c r="W33">
-        <v>0</v>
-      </c>
-      <c r="X33">
-        <v>0</v>
-      </c>
-      <c r="Y33">
-        <v>0</v>
-      </c>
-      <c r="Z33">
-        <v>0</v>
-      </c>
-      <c r="AA33">
-        <v>0</v>
-      </c>
-      <c r="AB33">
-        <v>0</v>
-      </c>
-      <c r="AC33">
-        <v>0</v>
-      </c>
-      <c r="AD33">
-        <v>0</v>
-      </c>
-      <c r="AE33">
-        <v>0</v>
-      </c>
-      <c r="AF33">
-        <v>0</v>
-      </c>
-      <c r="AG33">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ33">
-        <v>0</v>
-      </c>
-      <c r="AK33">
-        <v>0</v>
-      </c>
-      <c r="AL33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>-1</v>
-      </c>
-      <c r="AN33">
-        <v>-1</v>
-      </c>
-      <c r="AO33">
-        <v>-1</v>
-      </c>
-      <c r="AP33">
-        <v>-1</v>
-      </c>
-      <c r="AQ33">
-        <v>0</v>
-      </c>
-      <c r="AR33">
-        <v>0</v>
-      </c>
-      <c r="AS33">
-        <v>0</v>
-      </c>
-      <c r="AT33">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>2026-09-25 21:30:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>USA USL Championship</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>El Paso Locomotive</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Tulsa Roughnecks</t>
-        </is>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-      <c r="I34">
-        <v>0</v>
-      </c>
-      <c r="J34">
-        <v>0</v>
-      </c>
-      <c r="K34">
-        <v>0</v>
-      </c>
-      <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N34">
-        <v>1.75</v>
-      </c>
-      <c r="O34">
-        <v>3.54</v>
-      </c>
-      <c r="P34">
-        <v>3.99</v>
-      </c>
-      <c r="Q34">
-        <v>0</v>
-      </c>
-      <c r="R34">
-        <v>0</v>
-      </c>
-      <c r="S34">
-        <v>0</v>
-      </c>
-      <c r="T34">
-        <v>0</v>
-      </c>
-      <c r="U34">
-        <v>0</v>
-      </c>
-      <c r="V34">
-        <v>0</v>
-      </c>
-      <c r="W34">
-        <v>0</v>
-      </c>
-      <c r="X34">
-        <v>0</v>
-      </c>
-      <c r="Y34">
-        <v>0</v>
-      </c>
-      <c r="Z34">
-        <v>0</v>
-      </c>
-      <c r="AA34">
-        <v>1.84</v>
-      </c>
-      <c r="AB34">
-        <v>1.92</v>
-      </c>
-      <c r="AC34">
-        <v>0</v>
-      </c>
-      <c r="AD34">
-        <v>0</v>
-      </c>
-      <c r="AE34">
-        <v>0</v>
-      </c>
-      <c r="AF34">
-        <v>0</v>
-      </c>
-      <c r="AG34">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ34">
-        <v>0</v>
-      </c>
-      <c r="AK34">
-        <v>0</v>
-      </c>
-      <c r="AL34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>-1</v>
-      </c>
-      <c r="AN34">
-        <v>-1</v>
-      </c>
-      <c r="AO34">
-        <v>-1</v>
-      </c>
-      <c r="AP34">
-        <v>-1</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>2026-09-25 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35">
-        <v>0</v>
-      </c>
-      <c r="I35">
-        <v>0</v>
-      </c>
-      <c r="J35">
-        <v>0</v>
-      </c>
-      <c r="K35">
-        <v>0</v>
-      </c>
-      <c r="L35">
-        <v>0</v>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
-      <c r="O35">
-        <v>0</v>
-      </c>
-      <c r="P35">
-        <v>0</v>
-      </c>
-      <c r="Q35">
-        <v>0</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35">
-        <v>0</v>
-      </c>
-      <c r="T35">
-        <v>0</v>
-      </c>
-      <c r="U35">
-        <v>0</v>
-      </c>
-      <c r="V35">
-        <v>0</v>
-      </c>
-      <c r="W35">
-        <v>0</v>
-      </c>
-      <c r="X35">
-        <v>0</v>
-      </c>
-      <c r="Y35">
-        <v>0</v>
-      </c>
-      <c r="Z35">
-        <v>0</v>
-      </c>
-      <c r="AA35">
-        <v>0</v>
-      </c>
-      <c r="AB35">
-        <v>0</v>
-      </c>
-      <c r="AC35">
-        <v>0</v>
-      </c>
-      <c r="AD35">
-        <v>0</v>
-      </c>
-      <c r="AE35">
-        <v>0</v>
-      </c>
-      <c r="AF35">
-        <v>0</v>
-      </c>
-      <c r="AG35">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ35">
-        <v>0</v>
-      </c>
-      <c r="AK35">
-        <v>0</v>
-      </c>
-      <c r="AL35">
-        <v>0</v>
-      </c>
-      <c r="AM35">
-        <v>-1</v>
-      </c>
-      <c r="AN35">
-        <v>-1</v>
-      </c>
-      <c r="AO35">
-        <v>-1</v>
-      </c>
-      <c r="AP35">
-        <v>-1</v>
-      </c>
-      <c r="AQ35">
-        <v>0</v>
-      </c>
-      <c r="AR35">
-        <v>0</v>
-      </c>
-      <c r="AS35">
-        <v>0</v>
-      </c>
-      <c r="AT35">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="inlineStr">
         <is>
           <t>2026-09-25 22:00:00</t>
         </is>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1907,12 +1907,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G10">
@@ -1939,80 +1939,80 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.45</v>
+        <v>1.61</v>
       </c>
       <c r="O10">
-        <v>3.84</v>
+        <v>3.54</v>
       </c>
       <c r="P10">
-        <v>6.4</v>
+        <v>4.96</v>
       </c>
       <c r="Q10">
+        <v>2.45</v>
+      </c>
+      <c r="R10">
+        <v>1.97</v>
+      </c>
+      <c r="S10">
+        <v>1.41</v>
+      </c>
+      <c r="T10">
+        <v>2.55</v>
+      </c>
+      <c r="U10">
+        <v>2.87</v>
+      </c>
+      <c r="V10">
+        <v>1.35</v>
+      </c>
+      <c r="W10">
+        <v>1.03</v>
+      </c>
+      <c r="X10">
+        <v>1.04</v>
+      </c>
+      <c r="Y10">
+        <v>1.4</v>
+      </c>
+      <c r="Z10">
+        <v>2.9</v>
+      </c>
+      <c r="AA10">
+        <v>2.15</v>
+      </c>
+      <c r="AB10">
+        <v>1.6</v>
+      </c>
+      <c r="AC10">
+        <v>3.98</v>
+      </c>
+      <c r="AD10">
+        <v>1.2</v>
+      </c>
+      <c r="AE10">
+        <v>1.04</v>
+      </c>
+      <c r="AF10">
+        <v>2</v>
+      </c>
+      <c r="AG10">
+        <v>1.71</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ10">
+        <v>1.24</v>
+      </c>
+      <c r="AK10">
         <v>1.95</v>
-      </c>
-      <c r="R10">
-        <v>2.25</v>
-      </c>
-      <c r="S10">
-        <v>1.28</v>
-      </c>
-      <c r="T10">
-        <v>3.08</v>
-      </c>
-      <c r="U10">
-        <v>2.6</v>
-      </c>
-      <c r="V10">
-        <v>1.46</v>
-      </c>
-      <c r="W10">
-        <v>1.11</v>
-      </c>
-      <c r="X10">
-        <v>1.02</v>
-      </c>
-      <c r="Y10">
-        <v>1.19</v>
-      </c>
-      <c r="Z10">
-        <v>3.85</v>
-      </c>
-      <c r="AA10">
-        <v>1.79</v>
-      </c>
-      <c r="AB10">
-        <v>1.98</v>
-      </c>
-      <c r="AC10">
-        <v>3</v>
-      </c>
-      <c r="AD10">
-        <v>1.33</v>
-      </c>
-      <c r="AE10">
-        <v>1.1</v>
-      </c>
-      <c r="AF10">
-        <v>1.89</v>
-      </c>
-      <c r="AG10">
-        <v>1.8</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ10">
-        <v>1.13</v>
-      </c>
-      <c r="AK10">
-        <v>2.62</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.25</v>
+        <v>2.52</v>
       </c>
       <c r="O11">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>2.91</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="U11">
-        <v>3.24</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>2.83</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>1.97</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.61</v>
+        <v>1.45</v>
       </c>
       <c r="O12">
-        <v>3.54</v>
+        <v>3.84</v>
       </c>
       <c r="P12">
-        <v>4.96</v>
+        <v>6.4</v>
       </c>
       <c r="Q12">
-        <v>2.45</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>2.55</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.87</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>2.9</v>
+        <v>3.85</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>3.98</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AG12">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P13">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="U13">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
+        <v>2.31</v>
+      </c>
+      <c r="O15">
+        <v>3.2</v>
+      </c>
+      <c r="P15">
+        <v>2.68</v>
+      </c>
+      <c r="Q15">
+        <v>2.92</v>
+      </c>
+      <c r="R15">
         <v>2.25</v>
       </c>
-      <c r="O15">
-        <v>3.5</v>
-      </c>
-      <c r="P15">
-        <v>2.58</v>
-      </c>
-      <c r="Q15">
-        <v>2.62</v>
-      </c>
-      <c r="R15">
-        <v>2.45</v>
-      </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="X15">
         <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>5.1</v>
+        <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="AC15">
-        <v>2.13</v>
+        <v>2.83</v>
       </c>
       <c r="AD15">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AE15">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.7</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="O16">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="Q16">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S16">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.65</v>
+        <v>2.2</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>3.58</v>
+        <v>5.1</v>
       </c>
       <c r="AA16">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AB16">
-        <v>1.93</v>
+        <v>2.46</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="AD16">
-        <v>1.38</v>
+        <v>1.61</v>
       </c>
       <c r="AE16">
-        <v>1.09</v>
+        <v>1.26</v>
       </c>
       <c r="AF16">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="AG16">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AK16">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3415,55 +3415,55 @@
         <v>1.68</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3741,55 +3741,55 @@
         <v>2.12</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W21">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3904,55 +3904,55 @@
         <v>2.04</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V22">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W22">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X22">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z22">
-        <v>0</v>
+        <v>4.52</v>
       </c>
       <c r="AA22">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB22">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AC22">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AD22">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE22">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF22">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG22">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK22">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4230,55 +4230,55 @@
         <v>15.5</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="T24">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="U24">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W24">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA24">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AB24">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AC24">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AD24">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE24">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AF24">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AG24">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>3.99</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA27">
         <v>1.84</v>
@@ -4755,19 +4755,19 @@
         <v>1.92</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="O12">
-        <v>3.84</v>
+        <v>3.14</v>
       </c>
       <c r="P12">
-        <v>6.4</v>
+        <v>2.91</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>2.62</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>2.69</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y12">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="Z12">
-        <v>3.85</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
+        <v>1.97</v>
+      </c>
+      <c r="AB12">
         <v>1.79</v>
       </c>
-      <c r="AB12">
-        <v>1.98</v>
-      </c>
       <c r="AC12">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AD12">
+        <v>1.22</v>
+      </c>
+      <c r="AE12">
+        <v>1.05</v>
+      </c>
+      <c r="AF12">
+        <v>1.83</v>
+      </c>
+      <c r="AG12">
+        <v>1.86</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.33</v>
       </c>
-      <c r="AE12">
-        <v>1.1</v>
-      </c>
-      <c r="AF12">
-        <v>1.89</v>
-      </c>
-      <c r="AG12">
-        <v>1.8</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.13</v>
-      </c>
       <c r="AK12">
-        <v>2.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
+        <v>1.45</v>
+      </c>
+      <c r="O13">
+        <v>3.84</v>
+      </c>
+      <c r="P13">
+        <v>6.4</v>
+      </c>
+      <c r="Q13">
+        <v>1.95</v>
+      </c>
+      <c r="R13">
         <v>2.25</v>
       </c>
-      <c r="O13">
-        <v>3.14</v>
-      </c>
-      <c r="P13">
-        <v>2.91</v>
-      </c>
-      <c r="Q13">
+      <c r="S13">
+        <v>1.28</v>
+      </c>
+      <c r="T13">
+        <v>3.08</v>
+      </c>
+      <c r="U13">
+        <v>2.6</v>
+      </c>
+      <c r="V13">
+        <v>1.46</v>
+      </c>
+      <c r="W13">
+        <v>1.11</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.19</v>
+      </c>
+      <c r="Z13">
+        <v>3.85</v>
+      </c>
+      <c r="AA13">
+        <v>1.79</v>
+      </c>
+      <c r="AB13">
+        <v>1.98</v>
+      </c>
+      <c r="AC13">
+        <v>3</v>
+      </c>
+      <c r="AD13">
+        <v>1.33</v>
+      </c>
+      <c r="AE13">
+        <v>1.1</v>
+      </c>
+      <c r="AF13">
+        <v>1.89</v>
+      </c>
+      <c r="AG13">
+        <v>1.8</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.13</v>
+      </c>
+      <c r="AK13">
         <v>2.62</v>
-      </c>
-      <c r="R13">
-        <v>2.1</v>
-      </c>
-      <c r="S13">
-        <v>1.43</v>
-      </c>
-      <c r="T13">
-        <v>2.69</v>
-      </c>
-      <c r="U13">
-        <v>3.24</v>
-      </c>
-      <c r="V13">
-        <v>1.32</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>1.33</v>
-      </c>
-      <c r="Z13">
-        <v>2.83</v>
-      </c>
-      <c r="AA13">
-        <v>1.97</v>
-      </c>
-      <c r="AB13">
-        <v>1.79</v>
-      </c>
-      <c r="AC13">
-        <v>3.8</v>
-      </c>
-      <c r="AD13">
-        <v>1.22</v>
-      </c>
-      <c r="AE13">
-        <v>1.05</v>
-      </c>
-      <c r="AF13">
-        <v>1.83</v>
-      </c>
-      <c r="AG13">
-        <v>1.86</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.33</v>
-      </c>
-      <c r="AK13">
-        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P11">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T11">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK11">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,80 +2265,80 @@
         </is>
       </c>
       <c r="N12">
+        <v>1.45</v>
+      </c>
+      <c r="O12">
+        <v>3.84</v>
+      </c>
+      <c r="P12">
+        <v>6.4</v>
+      </c>
+      <c r="Q12">
+        <v>1.95</v>
+      </c>
+      <c r="R12">
         <v>2.25</v>
       </c>
-      <c r="O12">
-        <v>3.14</v>
-      </c>
-      <c r="P12">
-        <v>2.91</v>
-      </c>
-      <c r="Q12">
+      <c r="S12">
+        <v>1.28</v>
+      </c>
+      <c r="T12">
+        <v>3.08</v>
+      </c>
+      <c r="U12">
+        <v>2.6</v>
+      </c>
+      <c r="V12">
+        <v>1.46</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.19</v>
+      </c>
+      <c r="Z12">
+        <v>3.85</v>
+      </c>
+      <c r="AA12">
+        <v>1.79</v>
+      </c>
+      <c r="AB12">
+        <v>1.98</v>
+      </c>
+      <c r="AC12">
+        <v>3</v>
+      </c>
+      <c r="AD12">
+        <v>1.33</v>
+      </c>
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
+        <v>1.89</v>
+      </c>
+      <c r="AG12">
+        <v>1.8</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
+        <v>1.13</v>
+      </c>
+      <c r="AK12">
         <v>2.62</v>
-      </c>
-      <c r="R12">
-        <v>2.1</v>
-      </c>
-      <c r="S12">
-        <v>1.43</v>
-      </c>
-      <c r="T12">
-        <v>2.69</v>
-      </c>
-      <c r="U12">
-        <v>3.24</v>
-      </c>
-      <c r="V12">
-        <v>1.32</v>
-      </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.04</v>
-      </c>
-      <c r="Y12">
-        <v>1.33</v>
-      </c>
-      <c r="Z12">
-        <v>2.83</v>
-      </c>
-      <c r="AA12">
-        <v>1.97</v>
-      </c>
-      <c r="AB12">
-        <v>1.79</v>
-      </c>
-      <c r="AC12">
-        <v>3.8</v>
-      </c>
-      <c r="AD12">
-        <v>1.22</v>
-      </c>
-      <c r="AE12">
-        <v>1.05</v>
-      </c>
-      <c r="AF12">
-        <v>1.83</v>
-      </c>
-      <c r="AG12">
-        <v>1.86</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.33</v>
-      </c>
-      <c r="AK12">
-        <v>1.57</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="O13">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="P13">
-        <v>6.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q13">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z13">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA13">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AB13">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC13">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF13">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK13">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.25</v>
+        <v>1.51</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="P16">
-        <v>2.58</v>
+        <v>5.26</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="R16">
+        <v>2.38</v>
+      </c>
+      <c r="S16">
+        <v>1.28</v>
+      </c>
+      <c r="T16">
+        <v>3.12</v>
+      </c>
+      <c r="U16">
         <v>2.45</v>
       </c>
-      <c r="S16">
-        <v>1.22</v>
-      </c>
-      <c r="T16">
-        <v>3.5</v>
-      </c>
-      <c r="U16">
-        <v>2.2</v>
-      </c>
       <c r="V16">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
+        <v>1.12</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
         <v>1.17</v>
       </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
+      <c r="Z16">
+        <v>3.98</v>
+      </c>
+      <c r="AA16">
+        <v>1.67</v>
+      </c>
+      <c r="AB16">
+        <v>2.04</v>
+      </c>
+      <c r="AC16">
+        <v>2.69</v>
+      </c>
+      <c r="AD16">
+        <v>1.36</v>
+      </c>
+      <c r="AE16">
         <v>1.1</v>
       </c>
-      <c r="Z16">
-        <v>5.1</v>
-      </c>
-      <c r="AA16">
-        <v>1.43</v>
-      </c>
-      <c r="AB16">
-        <v>2.46</v>
-      </c>
-      <c r="AC16">
-        <v>2.13</v>
-      </c>
-      <c r="AD16">
-        <v>1.61</v>
-      </c>
-      <c r="AE16">
-        <v>1.26</v>
-      </c>
       <c r="AF16">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.7</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AK16">
-        <v>1.55</v>
+        <v>2.38</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.51</v>
+        <v>2.25</v>
       </c>
       <c r="O17">
-        <v>3.94</v>
+        <v>3.5</v>
       </c>
       <c r="P17">
-        <v>5.26</v>
+        <v>2.58</v>
       </c>
       <c r="Q17">
-        <v>2.18</v>
+        <v>2.62</v>
       </c>
       <c r="R17">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="S17">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T17">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="U17">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="V17">
+        <v>1.62</v>
+      </c>
+      <c r="W17">
+        <v>1.17</v>
+      </c>
+      <c r="X17">
+        <v>1.01</v>
+      </c>
+      <c r="Y17">
+        <v>1.1</v>
+      </c>
+      <c r="Z17">
+        <v>5.1</v>
+      </c>
+      <c r="AA17">
+        <v>1.43</v>
+      </c>
+      <c r="AB17">
+        <v>2.46</v>
+      </c>
+      <c r="AC17">
+        <v>2.13</v>
+      </c>
+      <c r="AD17">
+        <v>1.61</v>
+      </c>
+      <c r="AE17">
+        <v>1.26</v>
+      </c>
+      <c r="AF17">
         <v>1.44</v>
       </c>
-      <c r="W17">
-        <v>1.12</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.17</v>
-      </c>
-      <c r="Z17">
-        <v>3.98</v>
-      </c>
-      <c r="AA17">
-        <v>1.67</v>
-      </c>
-      <c r="AB17">
-        <v>2.04</v>
-      </c>
-      <c r="AC17">
-        <v>2.69</v>
-      </c>
-      <c r="AD17">
-        <v>1.36</v>
-      </c>
-      <c r="AE17">
-        <v>1.1</v>
-      </c>
-      <c r="AF17">
-        <v>1.67</v>
-      </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>2.38</v>
+        <v>1.55</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -635,19 +635,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>3.42</v>
+        <v>2.86</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.03</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>4.06</v>
+        <v>3.7</v>
       </c>
       <c r="R2">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="S2">
         <v>1.4</v>
@@ -656,10 +656,10 @@
         <v>2.7</v>
       </c>
       <c r="U2">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.02</v>
@@ -668,31 +668,31 @@
         <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="AA2">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AB2">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="AC2">
-        <v>3.82</v>
+        <v>3.58</v>
       </c>
       <c r="AD2">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.59</v>
+        <v>1.33</v>
       </c>
       <c r="AK2">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,80 +2102,80 @@
         </is>
       </c>
       <c r="N11">
+        <v>1.45</v>
+      </c>
+      <c r="O11">
+        <v>3.84</v>
+      </c>
+      <c r="P11">
+        <v>6.4</v>
+      </c>
+      <c r="Q11">
+        <v>1.95</v>
+      </c>
+      <c r="R11">
         <v>2.25</v>
       </c>
-      <c r="O11">
-        <v>3.14</v>
-      </c>
-      <c r="P11">
-        <v>2.91</v>
-      </c>
-      <c r="Q11">
+      <c r="S11">
+        <v>1.28</v>
+      </c>
+      <c r="T11">
+        <v>3.08</v>
+      </c>
+      <c r="U11">
+        <v>2.6</v>
+      </c>
+      <c r="V11">
+        <v>1.46</v>
+      </c>
+      <c r="W11">
+        <v>1.11</v>
+      </c>
+      <c r="X11">
+        <v>1.02</v>
+      </c>
+      <c r="Y11">
+        <v>1.19</v>
+      </c>
+      <c r="Z11">
+        <v>3.85</v>
+      </c>
+      <c r="AA11">
+        <v>1.79</v>
+      </c>
+      <c r="AB11">
+        <v>1.98</v>
+      </c>
+      <c r="AC11">
+        <v>3</v>
+      </c>
+      <c r="AD11">
+        <v>1.33</v>
+      </c>
+      <c r="AE11">
+        <v>1.1</v>
+      </c>
+      <c r="AF11">
+        <v>1.89</v>
+      </c>
+      <c r="AG11">
+        <v>1.8</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11">
+        <v>1.13</v>
+      </c>
+      <c r="AK11">
         <v>2.62</v>
-      </c>
-      <c r="R11">
-        <v>2.1</v>
-      </c>
-      <c r="S11">
-        <v>1.43</v>
-      </c>
-      <c r="T11">
-        <v>2.69</v>
-      </c>
-      <c r="U11">
-        <v>3.24</v>
-      </c>
-      <c r="V11">
-        <v>1.32</v>
-      </c>
-      <c r="W11">
-        <v>1.05</v>
-      </c>
-      <c r="X11">
-        <v>1.04</v>
-      </c>
-      <c r="Y11">
-        <v>1.33</v>
-      </c>
-      <c r="Z11">
-        <v>2.83</v>
-      </c>
-      <c r="AA11">
-        <v>1.97</v>
-      </c>
-      <c r="AB11">
-        <v>1.79</v>
-      </c>
-      <c r="AC11">
-        <v>3.8</v>
-      </c>
-      <c r="AD11">
-        <v>1.22</v>
-      </c>
-      <c r="AE11">
-        <v>1.05</v>
-      </c>
-      <c r="AF11">
-        <v>1.83</v>
-      </c>
-      <c r="AG11">
-        <v>1.86</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11">
-        <v>1.33</v>
-      </c>
-      <c r="AK11">
-        <v>1.57</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="P12">
-        <v>6.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF12">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK12">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.52</v>
+        <v>2.25</v>
       </c>
       <c r="O13">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="P13">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="Q13">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="R13">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S13">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T13">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="U13">
-        <v>2.76</v>
+        <v>3.24</v>
       </c>
       <c r="V13">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="W13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z13">
-        <v>3.3</v>
+        <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB13">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC13">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE13">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF13">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG13">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.88</v>
+        <v>2.08</v>
       </c>
       <c r="O14">
-        <v>3.48</v>
+        <v>3.42</v>
       </c>
       <c r="P14">
-        <v>3.48</v>
+        <v>3.11</v>
       </c>
       <c r="Q14">
         <v>2.5</v>
@@ -2609,28 +2609,28 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="U14">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="V14">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="AA14">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB14">
         <v>1.98</v>
@@ -2642,10 +2642,10 @@
         <v>1.34</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AF14">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG14">
         <v>2.15</v>
@@ -2664,7 +2664,7 @@
         <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2757,13 +2757,13 @@
         <v>2.31</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P15">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="Q15">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="R15">
         <v>2.25</v>
@@ -2775,13 +2775,13 @@
         <v>3.1</v>
       </c>
       <c r="U15">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W15">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
         <v>1.01</v>
@@ -2790,7 +2790,7 @@
         <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.58</v>
+        <v>3.84</v>
       </c>
       <c r="AA15">
         <v>1.75</v>
@@ -2802,7 +2802,7 @@
         <v>2.83</v>
       </c>
       <c r="AD15">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE15">
         <v>1.09</v>
@@ -2811,7 +2811,7 @@
         <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AK15">
         <v>1.5</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.51</v>
+        <v>2.21</v>
       </c>
       <c r="O16">
-        <v>3.94</v>
+        <v>3.54</v>
       </c>
       <c r="P16">
-        <v>5.26</v>
+        <v>2.7</v>
       </c>
       <c r="Q16">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="R16">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="S16">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.13</v>
       </c>
       <c r="V16">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>3.98</v>
+        <v>5.1</v>
       </c>
       <c r="AA16">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="AB16">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AC16">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD16">
+        <v>1.61</v>
+      </c>
+      <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
+        <v>1.44</v>
+      </c>
+      <c r="AG16">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
         <v>1.36</v>
       </c>
-      <c r="AE16">
-        <v>1.1</v>
-      </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.17</v>
-      </c>
       <c r="AK16">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="O17">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>2.58</v>
+        <v>4.53</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="R17">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="S17">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>1.02</v>
+      </c>
+      <c r="Y17">
         <v>1.17</v>
       </c>
-      <c r="X17">
-        <v>1.01</v>
-      </c>
-      <c r="Y17">
+      <c r="Z17">
+        <v>3.98</v>
+      </c>
+      <c r="AA17">
+        <v>1.72</v>
+      </c>
+      <c r="AB17">
+        <v>2.09</v>
+      </c>
+      <c r="AC17">
+        <v>2.69</v>
+      </c>
+      <c r="AD17">
+        <v>1.36</v>
+      </c>
+      <c r="AE17">
         <v>1.1</v>
       </c>
-      <c r="Z17">
-        <v>5.1</v>
-      </c>
-      <c r="AA17">
-        <v>1.43</v>
-      </c>
-      <c r="AB17">
-        <v>2.46</v>
-      </c>
-      <c r="AC17">
-        <v>2.13</v>
-      </c>
-      <c r="AD17">
-        <v>1.61</v>
-      </c>
-      <c r="AE17">
-        <v>1.26</v>
-      </c>
       <c r="AF17">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AK17">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1287,28 +1287,28 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4.38</v>
+        <v>4.64</v>
       </c>
       <c r="P6">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R6">
-        <v>2.61</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="V6">
         <v>1.56</v>
@@ -1323,22 +1323,22 @@
         <v>1.14</v>
       </c>
       <c r="Z6">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="AA6">
-        <v>1.55</v>
+        <v>1.47</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AC6">
-        <v>2.51</v>
+        <v>2.29</v>
       </c>
       <c r="AD6">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE6">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF6">
         <v>1.62</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AK6">
         <v>2.54</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.8</v>
+        <v>2.87</v>
       </c>
       <c r="O9">
         <v>3.1</v>
       </c>
       <c r="P9">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="Q9">
-        <v>3.96</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="S9">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="T9">
-        <v>2.5</v>
+        <v>3.12</v>
       </c>
       <c r="U9">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
-        <v>2.19</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
-        <v>1.7</v>
+        <v>2.11</v>
       </c>
       <c r="AC9">
-        <v>3.85</v>
+        <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="AE9">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>1.81</v>
+        <v>1.54</v>
       </c>
       <c r="AG9">
-        <v>1.85</v>
+        <v>2.32</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AK9">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU28"/>
+  <dimension ref="A1:AU27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2070,12 +2070,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G11">
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="O11">
-        <v>3.84</v>
+        <v>3.2</v>
       </c>
       <c r="P11">
-        <v>6.4</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
-        <v>1.95</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="T11">
-        <v>3.08</v>
+        <v>2.68</v>
       </c>
       <c r="U11">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.85</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
-        <v>1.79</v>
+        <v>2.03</v>
       </c>
       <c r="AB11">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AC11">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AK11">
-        <v>2.62</v>
+        <v>1.47</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>1.45</v>
       </c>
       <c r="O12">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="P12">
-        <v>2.45</v>
+        <v>6.4</v>
       </c>
       <c r="Q12">
-        <v>3.1</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="S12">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="T12">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="U12">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="V12">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X12">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="AA12">
-        <v>2.03</v>
+        <v>1.79</v>
       </c>
       <c r="AB12">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AD12">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE12">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>1.7</v>
+        <v>1.89</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK12">
-        <v>1.47</v>
+        <v>2.62</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>1.68</v>
       </c>
       <c r="Q19">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="R19">
         <v>2.5</v>
       </c>
       <c r="S19">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="T19">
         <v>4</v>
       </c>
       <c r="U19">
-        <v>2.1</v>
+        <v>2.19</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="W19">
         <v>1.15</v>
@@ -3445,25 +3445,25 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AB19">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AC19">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AD19">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="AE19">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AG19">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AK19">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,49 +3569,49 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="P20">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="Q20">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R20">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.08</v>
+        <v>3.17</v>
       </c>
       <c r="U20">
-        <v>2.6</v>
+        <v>2.69</v>
       </c>
       <c r="V20">
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1.01</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.5</v>
+        <v>3.82</v>
       </c>
       <c r="AA20">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AB20">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AC20">
         <v>2.83</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AK20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>3.44</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q21">
         <v>3.6</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="S21">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="U21">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="V21">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AB21">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AC21">
-        <v>2.73</v>
+        <v>2.59</v>
       </c>
       <c r="AD21">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="AE21">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF21">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AK21">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -4337,27 +4337,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="G25">
@@ -4384,13 +4384,13 @@
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q25">
         <v>0</v>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>2026-09-25 21:00:00</t>
+          <t>2026-09-25 21:30:00</t>
         </is>
       </c>
     </row>
@@ -4500,12 +4500,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="G26">
@@ -4547,64 +4547,64 @@
         </is>
       </c>
       <c r="N26">
-        <v>2.24</v>
+        <v>1.75</v>
       </c>
       <c r="O26">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>3.99</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH26" t="inlineStr">
         <is>
@@ -4617,10 +4617,10 @@
         </is>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AL26">
         <v>0</v>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>2026-09-25 21:30:00</t>
+          <t>2026-09-25 22:00:00</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Cavalry FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Supra du Québec</t>
         </is>
       </c>
       <c r="G27">
@@ -4710,64 +4710,64 @@
         </is>
       </c>
       <c r="N27">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>3.99</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="R27">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="V27">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W27">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="X27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AL27">
         <v>0</v>
@@ -4813,169 +4813,6 @@
         <v>0</v>
       </c>
       <c r="AU27" t="inlineStr">
-        <is>
-          <t>2026-09-25 22:00:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Canada Canadian Premier League</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Cavalry FC</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Supra du Québec</t>
-        </is>
-      </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28">
-        <v>0</v>
-      </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>0</v>
-      </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
-      <c r="O28">
-        <v>0</v>
-      </c>
-      <c r="P28">
-        <v>0</v>
-      </c>
-      <c r="Q28">
-        <v>0</v>
-      </c>
-      <c r="R28">
-        <v>0</v>
-      </c>
-      <c r="S28">
-        <v>0</v>
-      </c>
-      <c r="T28">
-        <v>0</v>
-      </c>
-      <c r="U28">
-        <v>0</v>
-      </c>
-      <c r="V28">
-        <v>0</v>
-      </c>
-      <c r="W28">
-        <v>0</v>
-      </c>
-      <c r="X28">
-        <v>0</v>
-      </c>
-      <c r="Y28">
-        <v>0</v>
-      </c>
-      <c r="Z28">
-        <v>0</v>
-      </c>
-      <c r="AA28">
-        <v>0</v>
-      </c>
-      <c r="AB28">
-        <v>0</v>
-      </c>
-      <c r="AC28">
-        <v>0</v>
-      </c>
-      <c r="AD28">
-        <v>0</v>
-      </c>
-      <c r="AE28">
-        <v>0</v>
-      </c>
-      <c r="AF28">
-        <v>0</v>
-      </c>
-      <c r="AG28">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ28">
-        <v>0</v>
-      </c>
-      <c r="AK28">
-        <v>0</v>
-      </c>
-      <c r="AL28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>-1</v>
-      </c>
-      <c r="AN28">
-        <v>-1</v>
-      </c>
-      <c r="AO28">
-        <v>-1</v>
-      </c>
-      <c r="AP28">
-        <v>-1</v>
-      </c>
-      <c r="AQ28">
-        <v>0</v>
-      </c>
-      <c r="AR28">
-        <v>0</v>
-      </c>
-      <c r="AS28">
-        <v>0</v>
-      </c>
-      <c r="AT28">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
         <is>
           <t>2026-09-25 22:00:00</t>
         </is>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1124,7 +1124,7 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O5">
         <v>3.3</v>
@@ -1133,13 +1133,13 @@
         <v>2.24</v>
       </c>
       <c r="Q5">
-        <v>3.56</v>
+        <v>3.15</v>
       </c>
       <c r="R5">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="T5">
         <v>2.94</v>
@@ -1148,40 +1148,40 @@
         <v>2.45</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
         <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="AB5">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="AD5">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AG5">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK5">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,31 +1287,31 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="O6">
-        <v>4.64</v>
+        <v>4.68</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R6">
         <v>2.5</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="T6">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U6">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W6">
         <v>1.14</v>
@@ -1320,31 +1320,31 @@
         <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.83</v>
+        <v>4.9</v>
       </c>
       <c r="AA6">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB6">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AC6">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="AD6">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AE6">
         <v>1.19</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AG6">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,80 +1613,80 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="O8">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="Q8">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="R8">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="S8">
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>2.94</v>
+        <v>3.21</v>
       </c>
       <c r="U8">
-        <v>2.57</v>
+        <v>2.51</v>
       </c>
       <c r="V8">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.58</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
+        <v>1.72</v>
+      </c>
+      <c r="AB8">
+        <v>1.96</v>
+      </c>
+      <c r="AC8">
+        <v>2.78</v>
+      </c>
+      <c r="AD8">
+        <v>1.34</v>
+      </c>
+      <c r="AE8">
+        <v>1.09</v>
+      </c>
+      <c r="AF8">
+        <v>1.63</v>
+      </c>
+      <c r="AG8">
+        <v>2.12</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8">
+        <v>1.22</v>
+      </c>
+      <c r="AK8">
         <v>1.76</v>
-      </c>
-      <c r="AB8">
-        <v>1.92</v>
-      </c>
-      <c r="AC8">
-        <v>2.92</v>
-      </c>
-      <c r="AD8">
-        <v>1.31</v>
-      </c>
-      <c r="AE8">
-        <v>1.13</v>
-      </c>
-      <c r="AF8">
-        <v>1.73</v>
-      </c>
-      <c r="AG8">
-        <v>1.98</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8">
-        <v>1.25</v>
-      </c>
-      <c r="AK8">
-        <v>2.05</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3243,52 +3243,52 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="P18">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="Q18">
         <v>3.47</v>
       </c>
       <c r="R18">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
         <v>1.18</v>
       </c>
       <c r="T18">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="U18">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="W18">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
         <v>6.15</v>
       </c>
       <c r="AA18">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AB18">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="AC18">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AD18">
         <v>1.79</v>
@@ -3297,10 +3297,10 @@
         <v>1.34</v>
       </c>
       <c r="AF18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AG18">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
         <v>1.34</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="O9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P9">
+        <v>2.3</v>
+      </c>
+      <c r="Q9">
+        <v>3.29</v>
+      </c>
+      <c r="R9">
         <v>2.25</v>
-      </c>
-      <c r="Q9">
-        <v>3.1</v>
-      </c>
-      <c r="R9">
-        <v>2.3</v>
       </c>
       <c r="S9">
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="U9">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="W9">
         <v>1.12</v>
@@ -1809,13 +1809,13 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="Z9">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
         <v>2.11</v>
@@ -1824,10 +1824,10 @@
         <v>2.59</v>
       </c>
       <c r="AD9">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
         <v>1.54</v>
@@ -1849,7 +1849,7 @@
         <v>1.53</v>
       </c>
       <c r="AK9">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,19 +1939,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="O10">
-        <v>3.54</v>
+        <v>3.4</v>
       </c>
       <c r="P10">
-        <v>4.96</v>
+        <v>3.9</v>
       </c>
       <c r="Q10">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="R10">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="S10">
         <v>1.41</v>
@@ -1960,7 +1960,7 @@
         <v>2.55</v>
       </c>
       <c r="U10">
-        <v>2.87</v>
+        <v>3.33</v>
       </c>
       <c r="V10">
         <v>1.35</v>
@@ -1969,34 +1969,34 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AB10">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC10">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="AD10">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE10">
         <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AG10">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>1.24</v>
       </c>
       <c r="AK10">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,22 +2102,22 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="O11">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="P11">
-        <v>2.45</v>
+        <v>2.73</v>
       </c>
       <c r="Q11">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S11">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
         <v>2.68</v>
@@ -2126,40 +2126,40 @@
         <v>2.76</v>
       </c>
       <c r="V11">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>2.03</v>
+        <v>1.95</v>
       </c>
       <c r="AB11">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AC11">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="AD11">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
         <v>1.06</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AK11">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,19 +2265,19 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="O12">
-        <v>3.84</v>
+        <v>4.15</v>
       </c>
       <c r="P12">
         <v>6.4</v>
       </c>
       <c r="Q12">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="S12">
         <v>1.28</v>
@@ -2292,31 +2292,31 @@
         <v>1.46</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.19</v>
       </c>
       <c r="Z12">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AA12">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AD12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
         <v>1.89</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK12">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,58 +2428,58 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O13">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="P13">
-        <v>2.91</v>
+        <v>3.25</v>
       </c>
       <c r="Q13">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="R13">
-        <v>2.1</v>
+        <v>1.97</v>
       </c>
       <c r="S13">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="T13">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="U13">
         <v>3.24</v>
       </c>
       <c r="V13">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
         <v>1.05</v>
       </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
       <c r="Y13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z13">
         <v>2.83</v>
       </c>
       <c r="AA13">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="AB13">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="AC13">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="AD13">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE13">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF13">
         <v>1.83</v>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AK13">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,25 +2591,25 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="O14">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="P14">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="Q14">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="R14">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T14">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
         <v>2.63</v>
@@ -2618,7 +2618,7 @@
         <v>1.46</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2627,19 +2627,19 @@
         <v>1.23</v>
       </c>
       <c r="Z14">
-        <v>3.94</v>
+        <v>3.91</v>
       </c>
       <c r="AA14">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AB14">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="AC14">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD14">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE14">
         <v>1.15</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,22 +2754,22 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="O15">
         <v>3.24</v>
       </c>
       <c r="P15">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="Q15">
-        <v>3.02</v>
+        <v>2.74</v>
       </c>
       <c r="R15">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="T15">
         <v>3.1</v>
@@ -2790,7 +2790,7 @@
         <v>1.21</v>
       </c>
       <c r="Z15">
-        <v>3.84</v>
+        <v>3.58</v>
       </c>
       <c r="AA15">
         <v>1.75</v>
@@ -2811,7 +2811,7 @@
         <v>1.6</v>
       </c>
       <c r="AG15">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.21</v>
+        <v>2.37</v>
       </c>
       <c r="O16">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="P16">
-        <v>2.7</v>
+        <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="R16">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="S16">
         <v>1.22</v>
@@ -2944,7 +2944,7 @@
         <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
         <v>1.02</v>
@@ -2953,10 +2953,10 @@
         <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>5.1</v>
+        <v>5.33</v>
       </c>
       <c r="AA16">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB16">
         <v>2.46</v>
@@ -2965,7 +2965,7 @@
         <v>2.2</v>
       </c>
       <c r="AD16">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AE16">
         <v>1.22</v>
@@ -2974,7 +2974,7 @@
         <v>1.44</v>
       </c>
       <c r="AG16">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK16">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="O17">
         <v>3.8</v>
       </c>
       <c r="P17">
-        <v>4.53</v>
+        <v>4.3</v>
       </c>
       <c r="Q17">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R17">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.12</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.98</v>
+        <v>3.93</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK17">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3418,13 +3418,13 @@
         <v>4.4</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S19">
         <v>1.23</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="U19">
         <v>2.19</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.2</v>
+        <v>2.07</v>
       </c>
       <c r="AK19">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3578,7 +3578,7 @@
         <v>5.8</v>
       </c>
       <c r="Q20">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="R20">
         <v>2.26</v>
@@ -3593,7 +3593,7 @@
         <v>2.69</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="W20">
         <v>1.1</v>
@@ -3611,22 +3611,22 @@
         <v>1.81</v>
       </c>
       <c r="AB20">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
         <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE20">
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.6</v>
       </c>
       <c r="P21">
         <v>1.92</v>
@@ -3750,7 +3750,7 @@
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
         <v>2.34</v>
@@ -3759,7 +3759,7 @@
         <v>1.48</v>
       </c>
       <c r="W21">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3771,19 +3771,19 @@
         <v>4.2</v>
       </c>
       <c r="AA21">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AC21">
         <v>2.59</v>
       </c>
       <c r="AD21">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AE21">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AF21">
         <v>1.54</v>
@@ -3895,80 +3895,80 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.98</v>
+        <v>2.43</v>
       </c>
       <c r="O22">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.04</v>
+        <v>2.43</v>
       </c>
       <c r="Q22">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R22">
-        <v>2.43</v>
+        <v>2.46</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="V22">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="W22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X22">
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="Z22">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="AA22">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AB22">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="AC22">
-        <v>2.49</v>
+        <v>2.39</v>
       </c>
       <c r="AD22">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AE22">
+        <v>1.22</v>
+      </c>
+      <c r="AF22">
+        <v>1.5</v>
+      </c>
+      <c r="AG22">
+        <v>2.47</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ22">
         <v>1.2</v>
       </c>
-      <c r="AF22">
-        <v>1.49</v>
-      </c>
-      <c r="AG22">
-        <v>2.42</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ22">
-        <v>1.22</v>
-      </c>
       <c r="AK22">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,28 +4058,28 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>5.27</v>
+        <v>5.5</v>
       </c>
       <c r="Q23">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="S23">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T23">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="U23">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V23">
         <v>1.33</v>
@@ -4097,13 +4097,13 @@
         <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AB23">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AC23">
-        <v>3.89</v>
+        <v>3.72</v>
       </c>
       <c r="AD23">
         <v>1.2</v>
@@ -4112,10 +4112,10 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AK23">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -4230,10 +4230,10 @@
         <v>15.5</v>
       </c>
       <c r="Q24">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="R24">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="S24">
         <v>1.17</v>
@@ -4242,10 +4242,10 @@
         <v>4.5</v>
       </c>
       <c r="U24">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="V24">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4257,28 +4257,28 @@
         <v>1.11</v>
       </c>
       <c r="Z24">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="AA24">
         <v>1.39</v>
       </c>
       <c r="AB24">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="AC24">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="AD24">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AE24">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AF24">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="AG24">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK24">
         <v>6</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.4</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
-        <v>4.15</v>
+        <v>3.25</v>
       </c>
       <c r="P12">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="Q12">
-        <v>1.85</v>
+        <v>2.82</v>
       </c>
       <c r="R12">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="T12">
-        <v>3.08</v>
+        <v>2.5</v>
       </c>
       <c r="U12">
-        <v>2.6</v>
+        <v>3.24</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>2.83</v>
       </c>
       <c r="AA12">
-        <v>1.76</v>
+        <v>2.15</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC12">
-        <v>2.9</v>
+        <v>3.58</v>
       </c>
       <c r="AD12">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AE12">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AK12">
-        <v>2.58</v>
+        <v>1.54</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="O13">
-        <v>3.25</v>
+        <v>4.15</v>
       </c>
       <c r="P13">
-        <v>3.25</v>
+        <v>6.4</v>
       </c>
       <c r="Q13">
-        <v>2.82</v>
+        <v>1.85</v>
       </c>
       <c r="R13">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="S13">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="T13">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="U13">
-        <v>3.24</v>
+        <v>2.6</v>
       </c>
       <c r="V13">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
+        <v>1.19</v>
+      </c>
+      <c r="Z13">
+        <v>3.8</v>
+      </c>
+      <c r="AA13">
+        <v>1.76</v>
+      </c>
+      <c r="AB13">
+        <v>1.95</v>
+      </c>
+      <c r="AC13">
+        <v>2.9</v>
+      </c>
+      <c r="AD13">
         <v>1.36</v>
       </c>
-      <c r="Z13">
-        <v>2.83</v>
-      </c>
-      <c r="AA13">
-        <v>2.15</v>
-      </c>
-      <c r="AB13">
-        <v>1.65</v>
-      </c>
-      <c r="AC13">
-        <v>3.58</v>
-      </c>
-      <c r="AD13">
-        <v>1.21</v>
-      </c>
       <c r="AE13">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="AG13">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AK13">
-        <v>1.54</v>
+        <v>2.58</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -3572,25 +3572,25 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.98</v>
+        <v>3.75</v>
       </c>
       <c r="P20">
         <v>5.8</v>
       </c>
       <c r="Q20">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="R20">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T20">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="U20">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="V20">
         <v>1.48</v>
@@ -3599,10 +3599,10 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z20">
         <v>3.82</v>
@@ -3614,10 +3614,10 @@
         <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD20">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AE20">
         <v>1.1</v>
@@ -3626,7 +3626,7 @@
         <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4061,49 +4061,49 @@
         <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.74</v>
       </c>
       <c r="P23">
-        <v>5.5</v>
+        <v>5.84</v>
       </c>
       <c r="Q23">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="R23">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="U23">
         <v>3.02</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W23">
         <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>2.92</v>
+        <v>3.03</v>
       </c>
       <c r="AA23">
         <v>2.14</v>
       </c>
       <c r="AB23">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="AD23">
         <v>1.2</v>
@@ -4112,10 +4112,10 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG23">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK23">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1127,10 +1127,10 @@
         <v>2.9</v>
       </c>
       <c r="O5">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="P5">
-        <v>2.24</v>
+        <v>2.15</v>
       </c>
       <c r="Q5">
         <v>3.15</v>
@@ -1145,10 +1145,10 @@
         <v>2.94</v>
       </c>
       <c r="U5">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="W5">
         <v>1.11</v>
@@ -1157,28 +1157,28 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z5">
         <v>3.84</v>
       </c>
       <c r="AA5">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="AB5">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AC5">
         <v>2.3</v>
       </c>
       <c r="AD5">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF5">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AG5">
         <v>1.95</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4.68</v>
+        <v>4.54</v>
       </c>
       <c r="P6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
         <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="W6">
         <v>1.14</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6">
         <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AA6">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AB6">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AC6">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AD6">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="AE6">
         <v>1.19</v>
       </c>
       <c r="AF6">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG6">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK6">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.86</v>
+        <v>2.05</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.48</v>
+        <v>2.66</v>
       </c>
       <c r="R8">
-        <v>2.16</v>
+        <v>2.31</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="T8">
         <v>3.21</v>
       </c>
       <c r="U8">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1.03</v>
@@ -1649,28 +1649,28 @@
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB8">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC8">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AG8">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1942,28 +1942,28 @@
         <v>1.78</v>
       </c>
       <c r="O10">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="P10">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q10">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R10">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="S10">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="T10">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="U10">
-        <v>3.33</v>
+        <v>2.96</v>
       </c>
       <c r="V10">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1972,25 +1972,25 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="Z10">
         <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AB10">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AC10">
-        <v>4.05</v>
+        <v>4.33</v>
       </c>
       <c r="AD10">
         <v>1.16</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF10">
         <v>2.01</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK10">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,55 +2102,55 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="O11">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="P11">
         <v>2.73</v>
       </c>
       <c r="Q11">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="R11">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="T11">
         <v>2.68</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X11">
         <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z11">
         <v>3.28</v>
       </c>
       <c r="AA11">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="AC11">
-        <v>3.14</v>
+        <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AE11">
         <v>1.06</v>
@@ -2277,22 +2277,22 @@
         <v>2.82</v>
       </c>
       <c r="R12">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="S12">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="T12">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U12">
         <v>3.24</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X12">
         <v>1.05</v>
@@ -2301,28 +2301,28 @@
         <v>1.36</v>
       </c>
       <c r="Z12">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA12">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AC12">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="AD12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK12">
         <v>1.54</v>
@@ -2428,13 +2428,13 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O13">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q13">
         <v>1.85</v>
@@ -2443,49 +2443,49 @@
         <v>2.26</v>
       </c>
       <c r="S13">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.08</v>
+        <v>3.18</v>
       </c>
       <c r="U13">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AC13">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AD13">
         <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.89</v>
+        <v>2.01</v>
       </c>
       <c r="AG13">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="O18">
         <v>3.8</v>
@@ -3252,22 +3252,22 @@
         <v>2</v>
       </c>
       <c r="Q18">
-        <v>3.47</v>
+        <v>3.1</v>
       </c>
       <c r="R18">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S18">
         <v>1.18</v>
       </c>
       <c r="T18">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="U18">
         <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W18">
         <v>1.22</v>
@@ -3276,16 +3276,16 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z18">
-        <v>6.15</v>
+        <v>6.2</v>
       </c>
       <c r="AA18">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AB18">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="AC18">
         <v>1.94</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AK18">
         <v>1.34</v>
@@ -3572,7 +3572,7 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P20">
         <v>5.8</v>
@@ -3584,10 +3584,10 @@
         <v>2.19</v>
       </c>
       <c r="S20">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="U20">
         <v>2.5</v>
@@ -3608,7 +3608,7 @@
         <v>3.82</v>
       </c>
       <c r="AA20">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
         <v>1.95</v>
@@ -4061,10 +4061,10 @@
         <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.74</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>5.84</v>
+        <v>5.25</v>
       </c>
       <c r="Q23">
         <v>2.17</v>
@@ -4088,7 +4088,7 @@
         <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.31</v>
@@ -4710,13 +4710,13 @@
         </is>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="P27">
-        <v>0</v>
+        <v>5.12</v>
       </c>
       <c r="Q27">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1785,7 +1785,7 @@
         <v>2.3</v>
       </c>
       <c r="Q9">
-        <v>3.29</v>
+        <v>3.2</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1794,7 +1794,7 @@
         <v>1.3</v>
       </c>
       <c r="T9">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
       <c r="U9">
         <v>2.47</v>
@@ -1803,25 +1803,25 @@
         <v>1.46</v>
       </c>
       <c r="W9">
-        <v>1.12</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.26</v>
+        <v>4.1</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AB9">
         <v>2.11</v>
       </c>
       <c r="AC9">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AD9">
         <v>1.44</v>
@@ -1833,7 +1833,7 @@
         <v>1.54</v>
       </c>
       <c r="AG9">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AK9">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2591,22 +2591,22 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O14">
         <v>3.44</v>
       </c>
       <c r="P14">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="Q14">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="R14">
         <v>2.15</v>
       </c>
       <c r="S14">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T14">
         <v>3.2</v>
@@ -2615,34 +2615,34 @@
         <v>2.63</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W14">
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.91</v>
+        <v>3.85</v>
       </c>
       <c r="AA14">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC14">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AD14">
         <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
         <v>1.62</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
         <v>1.53</v>
@@ -2760,7 +2760,7 @@
         <v>3.24</v>
       </c>
       <c r="P15">
-        <v>2.39</v>
+        <v>2.55</v>
       </c>
       <c r="Q15">
         <v>2.74</v>
@@ -2827,7 +2827,7 @@
         <v>1.5</v>
       </c>
       <c r="AK15">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2926,10 +2926,10 @@
         <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="R16">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S16">
         <v>1.22</v>
@@ -2944,7 +2944,7 @@
         <v>1.62</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="X16">
         <v>1.02</v>
@@ -2953,13 +2953,13 @@
         <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>5.33</v>
+        <v>5.34</v>
       </c>
       <c r="AA16">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AB16">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="AC16">
         <v>2.2</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="P17">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="R17">
         <v>2.23</v>
@@ -3110,13 +3110,13 @@
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
         <v>1.18</v>
       </c>
       <c r="Z17">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="AA17">
         <v>1.75</v>
@@ -3125,10 +3125,10 @@
         <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="AD17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AK17">
         <v>2</v>
@@ -3418,19 +3418,19 @@
         <v>4.4</v>
       </c>
       <c r="R19">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="S19">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="T19">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="U19">
         <v>2.19</v>
       </c>
       <c r="V19">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W19">
         <v>1.15</v>
@@ -3460,10 +3460,10 @@
         <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AG19">
-        <v>2.31</v>
+        <v>2.05</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>2.07</v>
       </c>
       <c r="AK19">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,61 +3732,61 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="O21">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="P21">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q21">
         <v>3.6</v>
       </c>
       <c r="R21">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="S21">
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="U21">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="V21">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="AC21">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="AD21">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE21">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="O22">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="Q22">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R22">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="U22">
         <v>2.25</v>
       </c>
       <c r="V22">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W22">
         <v>1.12</v>
@@ -3928,31 +3928,31 @@
         <v>1.01</v>
       </c>
       <c r="Y22">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA22">
+        <v>1.49</v>
+      </c>
+      <c r="AB22">
+        <v>2.31</v>
+      </c>
+      <c r="AC22">
+        <v>2.36</v>
+      </c>
+      <c r="AD22">
         <v>1.53</v>
       </c>
-      <c r="AB22">
-        <v>2.35</v>
-      </c>
-      <c r="AC22">
-        <v>2.39</v>
-      </c>
-      <c r="AD22">
-        <v>1.49</v>
-      </c>
       <c r="AE22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF22">
         <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4272,13 +4272,13 @@
         <v>1.7</v>
       </c>
       <c r="AE24">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AF24">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4749,10 +4749,10 @@
         <v>0</v>
       </c>
       <c r="AA27">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB27">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC27">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -3572,61 +3572,61 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
         <v>5.8</v>
       </c>
       <c r="Q20">
-        <v>1.97</v>
+        <v>2.12</v>
       </c>
       <c r="R20">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>3.02</v>
+        <v>2.82</v>
       </c>
       <c r="U20">
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="X20">
         <v>1</v>
       </c>
       <c r="Y20">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="AA20">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AB20">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AC20">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="AD20">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AG20">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.08</v>
       </c>
       <c r="AK20">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,61 +4058,61 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="P23">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="Q23">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="R23">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="T23">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U23">
-        <v>3.02</v>
+        <v>2.87</v>
       </c>
       <c r="V23">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X23">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y23">
         <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AA23">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="AB23">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC23">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="AD23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="AG23">
         <v>1.73</v>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AK23">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="O5">
-        <v>3.32</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>3.15</v>
+        <v>3.54</v>
       </c>
       <c r="R5">
         <v>2.05</v>
@@ -1145,37 +1145,37 @@
         <v>2.94</v>
       </c>
       <c r="U5">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V5">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="AA5">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB5">
-        <v>2.06</v>
+        <v>2.01</v>
       </c>
       <c r="AC5">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AE5">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
         <v>1.57</v>
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="O6">
-        <v>4.54</v>
+        <v>4</v>
       </c>
       <c r="P6">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="Q6">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="S6">
         <v>1.25</v>
@@ -1326,10 +1326,10 @@
         <v>4.8</v>
       </c>
       <c r="AA6">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AC6">
         <v>2.29</v>
@@ -1338,13 +1338,13 @@
         <v>1.52</v>
       </c>
       <c r="AE6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1622,25 +1622,25 @@
         <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="R8">
-        <v>2.31</v>
+        <v>2.19</v>
       </c>
       <c r="S8">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="U8">
         <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
         <v>1.03</v>
@@ -1649,13 +1649,13 @@
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AB8">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
         <v>2.83</v>
@@ -1686,7 +1686,7 @@
         <v>1.3</v>
       </c>
       <c r="AK8">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1939,25 +1939,25 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="O10">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P10">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q10">
         <v>2.5</v>
       </c>
       <c r="R10">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T10">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="U10">
         <v>2.96</v>
@@ -1972,28 +1972,28 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z10">
         <v>2.74</v>
       </c>
       <c r="AA10">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="AB10">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.33</v>
+        <v>4.05</v>
       </c>
       <c r="AD10">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG10">
         <v>1.7</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AK10">
         <v>1.85</v>
@@ -2111,19 +2111,19 @@
         <v>2.73</v>
       </c>
       <c r="Q11">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="S11">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.68</v>
+        <v>2.98</v>
       </c>
       <c r="U11">
-        <v>2.63</v>
+        <v>2.76</v>
       </c>
       <c r="V11">
         <v>1.35</v>
@@ -2138,19 +2138,19 @@
         <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="AA11">
         <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
         <v>3.3</v>
       </c>
       <c r="AD11">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AE11">
         <v>1.06</v>
@@ -2159,7 +2159,7 @@
         <v>1.68</v>
       </c>
       <c r="AG11">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK11">
         <v>1.45</v>
@@ -2265,31 +2265,31 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="O12">
         <v>3.25</v>
       </c>
       <c r="P12">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="Q12">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="R12">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="S12">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T12">
         <v>2.75</v>
       </c>
       <c r="U12">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="V12">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2298,31 +2298,31 @@
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Z12">
-        <v>2.81</v>
+        <v>2.95</v>
       </c>
       <c r="AA12">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB12">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC12">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="AD12">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK12">
         <v>1.54</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
-        <v>8.199999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="Q13">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="R13">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
         <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="U13">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="V13">
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="Z13">
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AC13">
         <v>2.83</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="AG13">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.17</v>
       </c>
       <c r="AK13">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="O18">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="P18">
         <v>2</v>
       </c>
       <c r="Q18">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R18">
         <v>2.63</v>
@@ -3261,7 +3261,7 @@
         <v>1.18</v>
       </c>
       <c r="T18">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="U18">
         <v>1.95</v>
@@ -3276,22 +3276,22 @@
         <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Z18">
         <v>6.2</v>
       </c>
       <c r="AA18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AB18">
-        <v>2.87</v>
+        <v>3.1</v>
       </c>
       <c r="AC18">
         <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AE18">
         <v>1.34</v>
@@ -3569,34 +3569,34 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="P20">
         <v>5.8</v>
       </c>
       <c r="Q20">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="R20">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="U20">
         <v>2.5</v>
       </c>
       <c r="V20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3608,7 +3608,7 @@
         <v>3.81</v>
       </c>
       <c r="AA20">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
         <v>2.02</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>2.7</v>
       </c>
       <c r="O21">
-        <v>3.38</v>
+        <v>3.35</v>
       </c>
       <c r="P21">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q21">
         <v>3.6</v>
@@ -3759,7 +3759,7 @@
         <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3774,10 +3774,10 @@
         <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AD21">
         <v>1.38</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
       <c r="AK21">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,34 +3895,34 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q22">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R22">
         <v>2.47</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.48</v>
+        <v>3.7</v>
       </c>
       <c r="U22">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="V22">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W22">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X22">
         <v>1.01</v>
@@ -3931,22 +3931,22 @@
         <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.6</v>
+        <v>4.61</v>
       </c>
       <c r="AA22">
         <v>1.49</v>
       </c>
       <c r="AB22">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AC22">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="AD22">
         <v>1.53</v>
       </c>
       <c r="AE22">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="AF22">
         <v>1.5</v>
@@ -3968,7 +3968,7 @@
         <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,37 +4058,37 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="O23">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="P23">
-        <v>4.65</v>
+        <v>5.75</v>
       </c>
       <c r="Q23">
         <v>2.19</v>
       </c>
       <c r="R23">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="U23">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="V23">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W23">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X23">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y23">
         <v>1.31</v>
@@ -4112,10 +4112,10 @@
         <v>1.03</v>
       </c>
       <c r="AF23">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,10 +4128,10 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1776,31 +1776,31 @@
         </is>
       </c>
       <c r="N9">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="O9">
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="Q9">
         <v>3.2</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="S9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>3.12</v>
       </c>
       <c r="U9">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="W9">
         <v>1.07</v>
@@ -1812,10 +1812,10 @@
         <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.1</v>
+        <v>4.28</v>
       </c>
       <c r="AA9">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB9">
         <v>2.11</v>
@@ -1824,10 +1824,10 @@
         <v>2.62</v>
       </c>
       <c r="AD9">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.54</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AK9">
         <v>1.44</v>
@@ -2108,7 +2108,7 @@
         <v>3.25</v>
       </c>
       <c r="P11">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2147,7 +2147,7 @@
         <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AD11">
         <v>1.27</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="O12">
         <v>3.25</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="P13">
         <v>8.449999999999999</v>
@@ -2455,7 +2455,7 @@
         <v>1.44</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
         <v>1.02</v>
@@ -2591,19 +2591,19 @@
         </is>
       </c>
       <c r="N14">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="O14">
-        <v>3.44</v>
+        <v>3.35</v>
       </c>
       <c r="P14">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="Q14">
-        <v>2.91</v>
+        <v>2.75</v>
       </c>
       <c r="R14">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
         <v>1.3</v>
@@ -2621,19 +2621,19 @@
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.24</v>
       </c>
       <c r="Z14">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB14">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
         <v>2.83</v>
@@ -2642,7 +2642,7 @@
         <v>1.33</v>
       </c>
       <c r="AE14">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
         <v>1.62</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AK14">
         <v>1.53</v>
@@ -2757,25 +2757,25 @@
         <v>2.55</v>
       </c>
       <c r="O15">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>2.55</v>
+        <v>2.4</v>
       </c>
       <c r="Q15">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="R15">
         <v>2.1</v>
       </c>
       <c r="S15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="V15">
         <v>1.44</v>
@@ -2784,7 +2784,7 @@
         <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y15">
         <v>1.21</v>
@@ -2796,7 +2796,7 @@
         <v>1.75</v>
       </c>
       <c r="AB15">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AC15">
         <v>2.83</v>
@@ -2808,7 +2808,7 @@
         <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG15">
         <v>2.14</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AK15">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.37</v>
+        <v>2.43</v>
       </c>
       <c r="O16">
         <v>3.52</v>
@@ -2926,7 +2926,7 @@
         <v>2.42</v>
       </c>
       <c r="Q16">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="R16">
         <v>2.52</v>
@@ -2935,10 +2935,10 @@
         <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="V16">
         <v>1.62</v>
@@ -2959,7 +2959,7 @@
         <v>1.47</v>
       </c>
       <c r="AB16">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="AC16">
         <v>2.2</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AK16">
         <v>1.44</v>
@@ -3080,16 +3080,16 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="O17">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Q17">
-        <v>2.34</v>
+        <v>2.08</v>
       </c>
       <c r="R17">
         <v>2.23</v>
@@ -3110,10 +3110,10 @@
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
         <v>3.88</v>
@@ -3125,7 +3125,7 @@
         <v>1.99</v>
       </c>
       <c r="AC17">
-        <v>2.84</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
         <v>1.36</v>
@@ -3137,7 +3137,7 @@
         <v>1.65</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3421,19 +3421,19 @@
         <v>2.42</v>
       </c>
       <c r="S19">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="T19">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="U19">
-        <v>2.19</v>
+        <v>1.86</v>
       </c>
       <c r="V19">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="W19">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3445,10 +3445,10 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AB19">
-        <v>2.42</v>
+        <v>2.55</v>
       </c>
       <c r="AC19">
         <v>2.18</v>
@@ -3460,10 +3460,10 @@
         <v>1.21</v>
       </c>
       <c r="AF19">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.05</v>
+        <v>2.31</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -4230,22 +4230,22 @@
         <v>15.5</v>
       </c>
       <c r="Q24">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R24">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="S24">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="U24">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4254,31 +4254,31 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="AC24">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AD24">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AE24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
         <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="AJ24">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK24">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1133,19 +1133,19 @@
         <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="R5">
         <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T5">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U5">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
         <v>1.49</v>
@@ -1163,13 +1163,13 @@
         <v>3</v>
       </c>
       <c r="AA5">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AB5">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="AC5">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
         <v>1.42</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AK5">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,13 +1287,13 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>1.91</v>
@@ -1311,16 +1311,16 @@
         <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="W6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
         <v>1.03</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="Z6">
         <v>4.8</v>
@@ -1329,19 +1329,19 @@
         <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AC6">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AD6">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF6">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="AG6">
         <v>2.05</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
         <v>2.5</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="Q8">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="R8">
         <v>2.19</v>
@@ -1631,13 +1631,13 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="U8">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1652,7 +1652,7 @@
         <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
         <v>1.96</v>
@@ -1667,10 +1667,10 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AG8">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1948,19 +1948,19 @@
         <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="R10">
         <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="T10">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="U10">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="V10">
         <v>1.33</v>
@@ -2277,7 +2277,7 @@
         <v>2.9</v>
       </c>
       <c r="R12">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="S12">
         <v>1.4</v>
@@ -2289,7 +2289,7 @@
         <v>2.99</v>
       </c>
       <c r="V12">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W12">
         <v>1.05</v>
@@ -2304,25 +2304,25 @@
         <v>2.95</v>
       </c>
       <c r="AA12">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AB12">
         <v>1.64</v>
       </c>
       <c r="AC12">
-        <v>3.58</v>
+        <v>3.7</v>
       </c>
       <c r="AD12">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE12">
         <v>1.04</v>
       </c>
       <c r="AF12">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AG12">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>1.8</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2470,13 +2470,13 @@
         <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC13">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD13">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
         <v>3.7</v>
@@ -3291,7 +3291,7 @@
         <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AE18">
         <v>1.34</v>
@@ -3418,19 +3418,19 @@
         <v>4.4</v>
       </c>
       <c r="R19">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S19">
         <v>1.22</v>
       </c>
       <c r="T19">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="U19">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V19">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W19">
         <v>1.14</v>
@@ -3451,19 +3451,19 @@
         <v>2.55</v>
       </c>
       <c r="AC19">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="AD19">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AE19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AF19">
         <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AK19">
         <v>1.2</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="P20">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>1.97</v>
@@ -3590,7 +3590,7 @@
         <v>2.97</v>
       </c>
       <c r="U20">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -3599,7 +3599,7 @@
         <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
@@ -3623,10 +3623,10 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AG20">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="O21">
         <v>3.35</v>
@@ -3759,7 +3759,7 @@
         <v>1.46</v>
       </c>
       <c r="W21">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X21">
         <v>1.02</v>
@@ -3768,7 +3768,7 @@
         <v>1.21</v>
       </c>
       <c r="Z21">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="AA21">
         <v>1.7</v>
@@ -3777,16 +3777,16 @@
         <v>2.1</v>
       </c>
       <c r="AC21">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD21">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AE21">
         <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.64</v>
+        <v>1.25</v>
       </c>
       <c r="AK21">
         <v>1.33</v>
@@ -3895,64 +3895,64 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.55</v>
+        <v>2.43</v>
       </c>
       <c r="O22">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P22">
-        <v>2.35</v>
+        <v>2</v>
       </c>
       <c r="Q22">
-        <v>3.08</v>
+        <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S22">
         <v>1.25</v>
       </c>
       <c r="T22">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="U22">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V22">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W22">
         <v>1.14</v>
       </c>
       <c r="X22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Z22">
-        <v>4.61</v>
+        <v>4.63</v>
       </c>
       <c r="AA22">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AB22">
+        <v>2.35</v>
+      </c>
+      <c r="AC22">
         <v>2.33</v>
       </c>
-      <c r="AC22">
-        <v>2.34</v>
-      </c>
       <c r="AD22">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AE22">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF22">
         <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3968,7 +3968,7 @@
         <v>1.19</v>
       </c>
       <c r="AK22">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,16 +4058,16 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="Q23">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="R23">
         <v>2.1</v>
@@ -4076,10 +4076,10 @@
         <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U23">
-        <v>2.86</v>
+        <v>3.02</v>
       </c>
       <c r="V23">
         <v>1.35</v>
@@ -4094,19 +4094,19 @@
         <v>1.31</v>
       </c>
       <c r="Z23">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB23">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC23">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AD23">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
         <v>2.25</v>
@@ -4233,7 +4233,7 @@
         <v>1.36</v>
       </c>
       <c r="R24">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="S24">
         <v>1.14</v>
@@ -4242,10 +4242,10 @@
         <v>4.8</v>
       </c>
       <c r="U24">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="V24">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="AA24">
         <v>1.36</v>
@@ -4266,19 +4266,19 @@
         <v>2.92</v>
       </c>
       <c r="AC24">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AD24">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AE24">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AF24">
         <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="P15">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="Q15">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="S15">
         <v>1.3</v>
@@ -2775,10 +2775,10 @@
         <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.06</v>
@@ -2793,7 +2793,7 @@
         <v>3.58</v>
       </c>
       <c r="AA15">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB15">
         <v>2.05</v>
@@ -2811,7 +2811,7 @@
         <v>1.62</v>
       </c>
       <c r="AG15">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
         <v>3.52</v>
       </c>
       <c r="P16">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="Q16">
-        <v>3.02</v>
+        <v>3.26</v>
       </c>
       <c r="R16">
         <v>2.52</v>
@@ -2938,7 +2938,7 @@
         <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
         <v>1.62</v>
@@ -2953,25 +2953,25 @@
         <v>1.1</v>
       </c>
       <c r="Z16">
-        <v>5.34</v>
+        <v>5.36</v>
       </c>
       <c r="AA16">
         <v>1.47</v>
       </c>
       <c r="AB16">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="AC16">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="AD16">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AE16">
         <v>1.22</v>
       </c>
       <c r="AF16">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG16">
         <v>2.62</v>
@@ -2987,7 +2987,7 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AK16">
         <v>1.44</v>
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="O17">
         <v>3.7</v>
       </c>
       <c r="P17">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
         <v>2.08</v>
@@ -3104,7 +3104,7 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
         <v>1.12</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="AA17">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE17">
         <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AK17">
         <v>2</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -3575,19 +3575,19 @@
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q20">
         <v>1.97</v>
       </c>
       <c r="R20">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="S20">
         <v>1.33</v>
       </c>
       <c r="T20">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="U20">
         <v>2.6</v>
@@ -3642,7 +3642,7 @@
         <v>1.18</v>
       </c>
       <c r="AK20">
-        <v>2.28</v>
+        <v>2.19</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="P23">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="Q23">
         <v>2.16</v>
@@ -4097,19 +4097,19 @@
         <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="AB23">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC23">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD23">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF23">
         <v>2.1</v>
@@ -4131,7 +4131,7 @@
         <v>1.24</v>
       </c>
       <c r="AK23">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AL23">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -1305,7 +1305,7 @@
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U6">
         <v>2.25</v>
@@ -1317,7 +1317,7 @@
         <v>1.13</v>
       </c>
       <c r="X6">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.19</v>
@@ -1329,7 +1329,7 @@
         <v>1.57</v>
       </c>
       <c r="AB6">
-        <v>2.21</v>
+        <v>2.38</v>
       </c>
       <c r="AC6">
         <v>2.35</v>
@@ -1338,7 +1338,7 @@
         <v>1.5</v>
       </c>
       <c r="AE6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AF6">
         <v>1.65</v>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="O8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
         <v>3.35</v>
@@ -1625,13 +1625,13 @@
         <v>2.55</v>
       </c>
       <c r="R8">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
-        <v>3.24</v>
+        <v>2.39</v>
       </c>
       <c r="U8">
         <v>2.51</v>
@@ -1643,7 +1643,7 @@
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y8">
         <v>1.19</v>
@@ -1667,10 +1667,10 @@
         <v>1.09</v>
       </c>
       <c r="AF8">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="AG8">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1788,7 +1788,7 @@
         <v>3.2</v>
       </c>
       <c r="R9">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="S9">
         <v>1.29</v>
@@ -1818,13 +1818,13 @@
         <v>1.7</v>
       </c>
       <c r="AB9">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AC9">
         <v>2.62</v>
       </c>
       <c r="AD9">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE9">
         <v>1.17</v>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.53</v>
+        <v>1.29</v>
       </c>
       <c r="AK9">
         <v>1.44</v>
@@ -1954,10 +1954,10 @@
         <v>1.94</v>
       </c>
       <c r="S10">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="U10">
         <v>2.95</v>
@@ -1990,13 +1990,13 @@
         <v>1.22</v>
       </c>
       <c r="AE10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG10">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2102,10 +2102,10 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="O11">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P11">
         <v>2.7</v>
@@ -2132,28 +2132,28 @@
         <v>1.03</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA11">
         <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="AD11">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
         <v>1.68</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="O12">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2431,7 +2431,7 @@
         <v>1.35</v>
       </c>
       <c r="O13">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="P13">
         <v>8.449999999999999</v>
@@ -2440,7 +2440,7 @@
         <v>1.8</v>
       </c>
       <c r="R13">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="S13">
         <v>1.33</v>
@@ -2470,13 +2470,13 @@
         <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
         <v>1.13</v>
@@ -2485,7 +2485,7 @@
         <v>2.04</v>
       </c>
       <c r="AG13">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U14">
         <v>2.63</v>
@@ -2624,7 +2624,7 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z14">
         <v>3.78</v>
@@ -2636,19 +2636,19 @@
         <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD14">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AF14">
         <v>1.62</v>
       </c>
       <c r="AG14">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AK14">
         <v>1.5</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.56</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>3.24</v>
+        <v>3.52</v>
       </c>
       <c r="P15">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
+        <v>3.26</v>
+      </c>
+      <c r="R15">
+        <v>2.4</v>
+      </c>
+      <c r="S15">
+        <v>1.22</v>
+      </c>
+      <c r="T15">
         <v>3.5</v>
       </c>
-      <c r="R15">
-        <v>2.11</v>
-      </c>
-      <c r="S15">
-        <v>1.3</v>
-      </c>
-      <c r="T15">
-        <v>3.2</v>
-      </c>
       <c r="U15">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>3.58</v>
+        <v>5.36</v>
       </c>
       <c r="AA15">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD15">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AG15">
-        <v>2.12</v>
+        <v>2.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q16">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>2.52</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
+        <v>1.45</v>
+      </c>
+      <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.21</v>
+      </c>
+      <c r="Z16">
+        <v>3.58</v>
+      </c>
+      <c r="AA16">
+        <v>1.8</v>
+      </c>
+      <c r="AB16">
+        <v>2.05</v>
+      </c>
+      <c r="AC16">
+        <v>2.83</v>
+      </c>
+      <c r="AD16">
+        <v>1.4</v>
+      </c>
+      <c r="AE16">
+        <v>1.13</v>
+      </c>
+      <c r="AF16">
         <v>1.62</v>
       </c>
-      <c r="W16">
-        <v>1.13</v>
-      </c>
-      <c r="X16">
-        <v>1.02</v>
-      </c>
-      <c r="Y16">
-        <v>1.1</v>
-      </c>
-      <c r="Z16">
-        <v>5.36</v>
-      </c>
-      <c r="AA16">
-        <v>1.47</v>
-      </c>
-      <c r="AB16">
-        <v>2.49</v>
-      </c>
-      <c r="AC16">
-        <v>2.19</v>
-      </c>
-      <c r="AD16">
-        <v>1.66</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
-      <c r="AF16">
-        <v>1.39</v>
-      </c>
       <c r="AG16">
-        <v>2.62</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3104,19 +3104,19 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
         <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.96</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
         <v>1.72</v>
@@ -3125,19 +3125,19 @@
         <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
         <v>2</v>
@@ -3243,10 +3243,10 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="O18">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="P18">
         <v>2</v>
@@ -3279,7 +3279,7 @@
         <v>1.07</v>
       </c>
       <c r="Z18">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA18">
         <v>1.36</v>
@@ -3291,13 +3291,13 @@
         <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AE18">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AF18">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG18">
         <v>3</v>
@@ -3415,10 +3415,10 @@
         <v>1.68</v>
       </c>
       <c r="Q19">
-        <v>4.4</v>
+        <v>4.32</v>
       </c>
       <c r="R19">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3427,13 +3427,13 @@
         <v>3.6</v>
       </c>
       <c r="U19">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="V19">
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3448,7 +3448,7 @@
         <v>1.45</v>
       </c>
       <c r="AB19">
-        <v>2.55</v>
+        <v>2.35</v>
       </c>
       <c r="AC19">
         <v>2.24</v>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.97</v>
+        <v>2.2</v>
       </c>
       <c r="AK19">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3575,7 +3575,7 @@
         <v>3.8</v>
       </c>
       <c r="P20">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="Q20">
         <v>1.97</v>
@@ -3614,7 +3614,7 @@
         <v>2.02</v>
       </c>
       <c r="AC20">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="AD20">
         <v>1.33</v>
@@ -3741,10 +3741,10 @@
         <v>2</v>
       </c>
       <c r="Q21">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="R21">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3774,7 +3774,7 @@
         <v>1.7</v>
       </c>
       <c r="AB21">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC21">
         <v>2.66</v>
@@ -3898,7 +3898,7 @@
         <v>2.43</v>
       </c>
       <c r="O22">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="P22">
         <v>2</v>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="O23">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="P23">
         <v>5.4</v>
@@ -4100,7 +4100,7 @@
         <v>2.11</v>
       </c>
       <c r="AB23">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AC23">
         <v>3.74</v>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK23">
         <v>2.2</v>
@@ -4230,7 +4230,7 @@
         <v>15.5</v>
       </c>
       <c r="Q24">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R24">
         <v>2.8</v>
@@ -4239,13 +4239,13 @@
         <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="U24">
         <v>1.85</v>
       </c>
       <c r="V24">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4269,7 +4269,7 @@
         <v>1.9</v>
       </c>
       <c r="AD24">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AE24">
         <v>1.25</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1812,10 +1812,10 @@
         <v>1.16</v>
       </c>
       <c r="Z9">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="AA9">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
         <v>2.05</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="O16">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.69</v>
+        <v>2.6</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="P17">
-        <v>3.9</v>
+        <v>2.37</v>
       </c>
       <c r="Q17">
-        <v>2.08</v>
+        <v>3.5</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>3.58</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AB17">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O15">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q15">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="V15">
+        <v>1.45</v>
+      </c>
+      <c r="W15">
+        <v>1.06</v>
+      </c>
+      <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.21</v>
+      </c>
+      <c r="Z15">
+        <v>3.58</v>
+      </c>
+      <c r="AA15">
+        <v>1.8</v>
+      </c>
+      <c r="AB15">
+        <v>2.05</v>
+      </c>
+      <c r="AC15">
+        <v>2.83</v>
+      </c>
+      <c r="AD15">
+        <v>1.4</v>
+      </c>
+      <c r="AE15">
+        <v>1.13</v>
+      </c>
+      <c r="AF15">
         <v>1.62</v>
       </c>
-      <c r="W15">
-        <v>1.13</v>
-      </c>
-      <c r="X15">
-        <v>1.01</v>
-      </c>
-      <c r="Y15">
-        <v>1.13</v>
-      </c>
-      <c r="Z15">
-        <v>5.36</v>
-      </c>
-      <c r="AA15">
-        <v>1.47</v>
-      </c>
-      <c r="AB15">
-        <v>2.7</v>
-      </c>
-      <c r="AC15">
-        <v>2.19</v>
-      </c>
-      <c r="AD15">
-        <v>1.65</v>
-      </c>
-      <c r="AE15">
-        <v>1.22</v>
-      </c>
-      <c r="AF15">
+      <c r="AG15">
+        <v>2.25</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
+        <v>1.25</v>
+      </c>
+      <c r="AK15">
         <v>1.4</v>
-      </c>
-      <c r="AG15">
-        <v>2.75</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.53</v>
-      </c>
-      <c r="AK15">
-        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.69</v>
+        <v>2.43</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="P16">
-        <v>3.9</v>
+        <v>2.38</v>
       </c>
       <c r="Q16">
-        <v>2.08</v>
+        <v>3.26</v>
       </c>
       <c r="R16">
-        <v>2.23</v>
+        <v>2.4</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.12</v>
       </c>
       <c r="V16">
+        <v>1.62</v>
+      </c>
+      <c r="W16">
+        <v>1.13</v>
+      </c>
+      <c r="X16">
+        <v>1.01</v>
+      </c>
+      <c r="Y16">
+        <v>1.13</v>
+      </c>
+      <c r="Z16">
+        <v>5.36</v>
+      </c>
+      <c r="AA16">
+        <v>1.47</v>
+      </c>
+      <c r="AB16">
+        <v>2.7</v>
+      </c>
+      <c r="AC16">
+        <v>2.19</v>
+      </c>
+      <c r="AD16">
+        <v>1.65</v>
+      </c>
+      <c r="AE16">
+        <v>1.22</v>
+      </c>
+      <c r="AF16">
+        <v>1.4</v>
+      </c>
+      <c r="AG16">
+        <v>2.75</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.53</v>
+      </c>
+      <c r="AK16">
         <v>1.44</v>
-      </c>
-      <c r="W16">
-        <v>1.12</v>
-      </c>
-      <c r="X16">
-        <v>1.02</v>
-      </c>
-      <c r="Y16">
-        <v>1.22</v>
-      </c>
-      <c r="Z16">
-        <v>4.2</v>
-      </c>
-      <c r="AA16">
-        <v>1.72</v>
-      </c>
-      <c r="AB16">
-        <v>2.03</v>
-      </c>
-      <c r="AC16">
-        <v>2.88</v>
-      </c>
-      <c r="AD16">
-        <v>1.4</v>
-      </c>
-      <c r="AE16">
-        <v>1.14</v>
-      </c>
-      <c r="AF16">
-        <v>1.67</v>
-      </c>
-      <c r="AG16">
-        <v>2.1</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.19</v>
-      </c>
-      <c r="AK16">
-        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.6</v>
+        <v>1.69</v>
       </c>
       <c r="O17">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="P17">
-        <v>2.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="R17">
-        <v>2.11</v>
+        <v>2.23</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.65</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.58</v>
+        <v>4.2</v>
       </c>
       <c r="AA17">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="AC17">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
         <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK17">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1145,10 +1145,10 @@
         <v>2.99</v>
       </c>
       <c r="U5">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="V5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1160,16 +1160,16 @@
         <v>1.18</v>
       </c>
       <c r="Z5">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AA5">
         <v>1.68</v>
       </c>
       <c r="AB5">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AC5">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="AD5">
         <v>1.42</v>
@@ -1181,7 +1181,7 @@
         <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Q6">
         <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.32</v>
+        <v>2.39</v>
       </c>
       <c r="S6">
         <v>1.25</v>
       </c>
       <c r="T6">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
         <v>2.25</v>
@@ -1320,7 +1320,7 @@
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
         <v>4.8</v>
@@ -1332,16 +1332,16 @@
         <v>2.38</v>
       </c>
       <c r="AC6">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="AD6">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AE6">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AG6">
         <v>2.05</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AK6">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.6</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="P15">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
+        <v>3.26</v>
+      </c>
+      <c r="R15">
+        <v>2.4</v>
+      </c>
+      <c r="S15">
+        <v>1.22</v>
+      </c>
+      <c r="T15">
         <v>3.5</v>
       </c>
-      <c r="R15">
-        <v>2.11</v>
-      </c>
-      <c r="S15">
-        <v>1.3</v>
-      </c>
-      <c r="T15">
-        <v>3.2</v>
-      </c>
       <c r="U15">
-        <v>2.65</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y15">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>3.58</v>
+        <v>5.36</v>
       </c>
       <c r="AA15">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AB15">
-        <v>2.05</v>
+        <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.83</v>
+        <v>2.19</v>
       </c>
       <c r="AD15">
+        <v>1.65</v>
+      </c>
+      <c r="AE15">
+        <v>1.22</v>
+      </c>
+      <c r="AF15">
         <v>1.4</v>
       </c>
-      <c r="AE15">
-        <v>1.13</v>
-      </c>
-      <c r="AF15">
-        <v>1.62</v>
-      </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,80 +2917,80 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="O16">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="P16">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="Q16">
-        <v>3.26</v>
+        <v>3.5</v>
       </c>
       <c r="R16">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="S16">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="V16">
+        <v>1.45</v>
+      </c>
+      <c r="W16">
+        <v>1.06</v>
+      </c>
+      <c r="X16">
+        <v>1.03</v>
+      </c>
+      <c r="Y16">
+        <v>1.21</v>
+      </c>
+      <c r="Z16">
+        <v>3.58</v>
+      </c>
+      <c r="AA16">
+        <v>1.8</v>
+      </c>
+      <c r="AB16">
+        <v>2.05</v>
+      </c>
+      <c r="AC16">
+        <v>2.83</v>
+      </c>
+      <c r="AD16">
+        <v>1.4</v>
+      </c>
+      <c r="AE16">
+        <v>1.13</v>
+      </c>
+      <c r="AF16">
         <v>1.62</v>
       </c>
-      <c r="W16">
-        <v>1.13</v>
-      </c>
-      <c r="X16">
-        <v>1.01</v>
-      </c>
-      <c r="Y16">
-        <v>1.13</v>
-      </c>
-      <c r="Z16">
-        <v>5.36</v>
-      </c>
-      <c r="AA16">
-        <v>1.47</v>
-      </c>
-      <c r="AB16">
-        <v>2.7</v>
-      </c>
-      <c r="AC16">
-        <v>2.19</v>
-      </c>
-      <c r="AD16">
-        <v>1.65</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
-      <c r="AF16">
+      <c r="AG16">
+        <v>2.25</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16">
+        <v>1.25</v>
+      </c>
+      <c r="AK16">
         <v>1.4</v>
-      </c>
-      <c r="AG16">
-        <v>2.75</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16">
-        <v>1.53</v>
-      </c>
-      <c r="AK16">
-        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3744,7 +3744,7 @@
         <v>3.4</v>
       </c>
       <c r="R21">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3765,16 +3765,16 @@
         <v>1.02</v>
       </c>
       <c r="Y21">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AA21">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AB21">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AC21">
         <v>2.66</v>
@@ -3783,10 +3783,10 @@
         <v>1.37</v>
       </c>
       <c r="AE21">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK21">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,31 +3895,31 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="O22">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P22">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="Q22">
         <v>3.4</v>
       </c>
       <c r="R22">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T22">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="U22">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Z22">
-        <v>4.63</v>
+        <v>4.93</v>
       </c>
       <c r="AA22">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AB22">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AC22">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AD22">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="AE22">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AF22">
         <v>1.5</v>
       </c>
       <c r="AG22">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AK22">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL22">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>3.03</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -650,19 +650,19 @@
         <v>2.05</v>
       </c>
       <c r="S2">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="T2">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="U2">
-        <v>3.04</v>
+        <v>2.4</v>
       </c>
       <c r="V2">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="W2">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X2">
         <v>1.03</v>
@@ -671,28 +671,28 @@
         <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA2">
         <v>2.04</v>
       </c>
       <c r="AB2">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AC2">
-        <v>3.58</v>
+        <v>2.74</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AE2">
         <v>1.06</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AG2">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="AK2">
         <v>1.3</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>1.96</v>
+        <v>2.13</v>
       </c>
       <c r="O8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P8">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="Q8">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="S8">
         <v>1.28</v>
       </c>
       <c r="T8">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="U8">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W8">
         <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.82</v>
+        <v>3.76</v>
       </c>
       <c r="AA8">
+        <v>1.59</v>
+      </c>
+      <c r="AB8">
         <v>1.75</v>
       </c>
-      <c r="AB8">
-        <v>1.96</v>
-      </c>
       <c r="AC8">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AF8">
         <v>1.47</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>2.37</v>
       </c>
       <c r="Q9">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1794,7 +1794,7 @@
         <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="U9">
         <v>2.38</v>
@@ -1809,7 +1809,7 @@
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="Z9">
         <v>4.32</v>
@@ -1818,7 +1818,7 @@
         <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC9">
         <v>2.62</v>
@@ -1827,7 +1827,7 @@
         <v>1.4</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
         <v>1.54</v>
@@ -2012,7 +2012,7 @@
         <v>1.3</v>
       </c>
       <c r="AK10">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2114,13 +2114,13 @@
         <v>3</v>
       </c>
       <c r="R11">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S11">
         <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="U11">
         <v>2.76</v>
@@ -2144,7 +2144,7 @@
         <v>1.88</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AC11">
         <v>3.25</v>
@@ -2268,7 +2268,7 @@
         <v>2.15</v>
       </c>
       <c r="O12">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="P12">
         <v>3</v>
@@ -2298,10 +2298,10 @@
         <v>1.05</v>
       </c>
       <c r="Y12">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="Z12">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="AA12">
         <v>2.1</v>
@@ -2431,25 +2431,25 @@
         <v>1.35</v>
       </c>
       <c r="O13">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="P13">
-        <v>8.449999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="Q13">
         <v>1.8</v>
       </c>
       <c r="R13">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S13">
         <v>1.33</v>
       </c>
       <c r="T13">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="U13">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="V13">
         <v>1.44</v>
@@ -2461,7 +2461,7 @@
         <v>1.02</v>
       </c>
       <c r="Y13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z13">
         <v>3.8</v>
@@ -2473,7 +2473,7 @@
         <v>1.94</v>
       </c>
       <c r="AC13">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AD13">
         <v>1.4</v>
@@ -2603,7 +2603,7 @@
         <v>2.75</v>
       </c>
       <c r="R14">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="S14">
         <v>1.3</v>
@@ -2615,7 +2615,7 @@
         <v>2.63</v>
       </c>
       <c r="V14">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W14">
         <v>1.1</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
         <v>1.5</v>
@@ -2763,49 +2763,49 @@
         <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="S15">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W15">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y15">
         <v>1.13</v>
       </c>
       <c r="Z15">
-        <v>5.36</v>
+        <v>6</v>
       </c>
       <c r="AA15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB15">
         <v>2.7</v>
       </c>
       <c r="AC15">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AD15">
         <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AF15">
         <v>1.4</v>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="AK15">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="O16">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R16">
-        <v>2.11</v>
+        <v>2.28</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2938,7 +2938,7 @@
         <v>3.2</v>
       </c>
       <c r="U16">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="V16">
         <v>1.45</v>
@@ -2956,13 +2956,13 @@
         <v>3.58</v>
       </c>
       <c r="AA16">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB16">
         <v>2.05</v>
       </c>
       <c r="AC16">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
         <v>1.4</v>
@@ -2990,7 +2990,7 @@
         <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,7 +3080,7 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="O17">
         <v>3.7</v>
@@ -3089,10 +3089,10 @@
         <v>3.9</v>
       </c>
       <c r="Q17">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="R17">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
         <v>1.3</v>
@@ -3104,40 +3104,40 @@
         <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
         <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z17">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="AA17">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="AB17">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE17">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
+        <v>3.91</v>
+      </c>
+      <c r="O19">
         <v>3.95</v>
-      </c>
-      <c r="O19">
-        <v>3.86</v>
       </c>
       <c r="P19">
         <v>1.68</v>
       </c>
       <c r="Q19">
-        <v>4.32</v>
+        <v>3.8</v>
       </c>
       <c r="R19">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3439,10 +3439,10 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AA19">
         <v>1.45</v>
@@ -3572,16 +3572,16 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="P20">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>1.97</v>
       </c>
       <c r="R20">
-        <v>2.21</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
         <v>1.33</v>
@@ -3602,31 +3602,31 @@
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z20">
-        <v>3.81</v>
+        <v>3.92</v>
       </c>
       <c r="AA20">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AB20">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AC20">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="AD20">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE20">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG20">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AK20">
         <v>2.19</v>
@@ -4058,31 +4058,31 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="O23">
         <v>3.6</v>
       </c>
       <c r="P23">
-        <v>5.4</v>
+        <v>5.73</v>
       </c>
       <c r="Q23">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R23">
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T23">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="U23">
         <v>3.02</v>
       </c>
       <c r="V23">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4097,25 +4097,25 @@
         <v>2.92</v>
       </c>
       <c r="AA23">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AB23">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AC23">
-        <v>3.74</v>
+        <v>3.58</v>
       </c>
       <c r="AD23">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="AE23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF23">
         <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         </is>
       </c>
       <c r="AJ23">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK23">
         <v>2.2</v>
@@ -4230,22 +4230,22 @@
         <v>15.5</v>
       </c>
       <c r="Q24">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R24">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="S24">
         <v>1.14</v>
       </c>
       <c r="T24">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="U24">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="V24">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4254,10 +4254,10 @@
         <v>1.01</v>
       </c>
       <c r="Y24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z24">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AA24">
         <v>1.36</v>
@@ -4266,10 +4266,10 @@
         <v>2.92</v>
       </c>
       <c r="AC24">
-        <v>1.9</v>
+        <v>1.97</v>
       </c>
       <c r="AD24">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE24">
         <v>1.25</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -2233,12 +2233,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G12">
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>2.15</v>
+        <v>1.35</v>
       </c>
       <c r="O12">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="P12">
-        <v>3</v>
+        <v>8.9</v>
       </c>
       <c r="Q12">
+        <v>1.8</v>
+      </c>
+      <c r="R12">
+        <v>2.4</v>
+      </c>
+      <c r="S12">
+        <v>1.33</v>
+      </c>
+      <c r="T12">
+        <v>3.21</v>
+      </c>
+      <c r="U12">
+        <v>2.68</v>
+      </c>
+      <c r="V12">
+        <v>1.44</v>
+      </c>
+      <c r="W12">
+        <v>1.11</v>
+      </c>
+      <c r="X12">
+        <v>1.02</v>
+      </c>
+      <c r="Y12">
+        <v>1.25</v>
+      </c>
+      <c r="Z12">
+        <v>3.8</v>
+      </c>
+      <c r="AA12">
+        <v>1.75</v>
+      </c>
+      <c r="AB12">
+        <v>1.94</v>
+      </c>
+      <c r="AC12">
         <v>2.9</v>
       </c>
-      <c r="R12">
-        <v>1.96</v>
-      </c>
-      <c r="S12">
+      <c r="AD12">
         <v>1.4</v>
       </c>
-      <c r="T12">
-        <v>2.75</v>
-      </c>
-      <c r="U12">
-        <v>2.99</v>
-      </c>
-      <c r="V12">
-        <v>1.34</v>
-      </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.05</v>
-      </c>
-      <c r="Y12">
-        <v>1.38</v>
-      </c>
-      <c r="Z12">
-        <v>2.97</v>
-      </c>
-      <c r="AA12">
-        <v>2.1</v>
-      </c>
-      <c r="AB12">
-        <v>1.64</v>
-      </c>
-      <c r="AC12">
-        <v>3.7</v>
-      </c>
-      <c r="AD12">
-        <v>1.2</v>
-      </c>
       <c r="AE12">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AF12">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="AG12">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK12">
-        <v>1.54</v>
+        <v>2.83</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G13">
@@ -2428,80 +2428,80 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="O13">
-        <v>4.5</v>
+        <v>3.05</v>
       </c>
       <c r="P13">
-        <v>8.9</v>
+        <v>3</v>
       </c>
       <c r="Q13">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="R13">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="S13">
+        <v>1.4</v>
+      </c>
+      <c r="T13">
+        <v>2.75</v>
+      </c>
+      <c r="U13">
+        <v>2.99</v>
+      </c>
+      <c r="V13">
+        <v>1.34</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.05</v>
+      </c>
+      <c r="Y13">
+        <v>1.38</v>
+      </c>
+      <c r="Z13">
+        <v>2.97</v>
+      </c>
+      <c r="AA13">
+        <v>2.1</v>
+      </c>
+      <c r="AB13">
+        <v>1.64</v>
+      </c>
+      <c r="AC13">
+        <v>3.7</v>
+      </c>
+      <c r="AD13">
+        <v>1.2</v>
+      </c>
+      <c r="AE13">
+        <v>1.04</v>
+      </c>
+      <c r="AF13">
+        <v>1.84</v>
+      </c>
+      <c r="AG13">
+        <v>1.85</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ13">
         <v>1.33</v>
       </c>
-      <c r="T13">
-        <v>3.21</v>
-      </c>
-      <c r="U13">
-        <v>2.68</v>
-      </c>
-      <c r="V13">
-        <v>1.44</v>
-      </c>
-      <c r="W13">
-        <v>1.11</v>
-      </c>
-      <c r="X13">
-        <v>1.02</v>
-      </c>
-      <c r="Y13">
-        <v>1.25</v>
-      </c>
-      <c r="Z13">
-        <v>3.8</v>
-      </c>
-      <c r="AA13">
-        <v>1.75</v>
-      </c>
-      <c r="AB13">
-        <v>1.94</v>
-      </c>
-      <c r="AC13">
-        <v>2.9</v>
-      </c>
-      <c r="AD13">
-        <v>1.4</v>
-      </c>
-      <c r="AE13">
-        <v>1.13</v>
-      </c>
-      <c r="AF13">
-        <v>2.04</v>
-      </c>
-      <c r="AG13">
-        <v>1.73</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.17</v>
-      </c>
       <c r="AK13">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="AL13">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -631,17 +631,17 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="O3">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="U3">
-        <v>2.76</v>
+        <v>2.89</v>
       </c>
       <c r="V3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W3">
         <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="AA3">
         <v>2</v>
       </c>
       <c r="AB3">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC3">
-        <v>3.28</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
         <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AK3">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -1133,7 +1133,7 @@
         <v>2.28</v>
       </c>
       <c r="Q5">
-        <v>3.53</v>
+        <v>3.58</v>
       </c>
       <c r="R5">
         <v>2.05</v>
@@ -1145,7 +1145,7 @@
         <v>2.99</v>
       </c>
       <c r="U5">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="V5">
         <v>1.5</v>
@@ -1166,13 +1166,13 @@
         <v>1.68</v>
       </c>
       <c r="AB5">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AC5">
         <v>2.77</v>
       </c>
       <c r="AD5">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE5">
         <v>1.11</v>
@@ -1181,7 +1181,7 @@
         <v>1.57</v>
       </c>
       <c r="AG5">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1290,16 +1290,16 @@
         <v>1.5</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>4.5</v>
       </c>
       <c r="P6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Q6">
         <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="S6">
         <v>1.25</v>
@@ -1311,7 +1311,7 @@
         <v>2.25</v>
       </c>
       <c r="V6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="W6">
         <v>1.13</v>
@@ -1326,10 +1326,10 @@
         <v>4.8</v>
       </c>
       <c r="AA6">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AB6">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AC6">
         <v>2.38</v>
@@ -1341,7 +1341,7 @@
         <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AG6">
         <v>2.05</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="P16">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="Q16">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="R16">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S16">
         <v>1.3</v>
       </c>
       <c r="T16">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U16">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="V16">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y16">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z16">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA16">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC16">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD16">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
         <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AK16">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="O17">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.9</v>
+        <v>2.15</v>
       </c>
       <c r="Q17">
-        <v>2.11</v>
+        <v>3.2</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W17">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z17">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA17">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="AB17">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD17">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE17">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF17">
         <v>1.62</v>
       </c>
       <c r="AG17">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK17">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.87</v>
+        <v>2.95</v>
       </c>
       <c r="O18">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="P18">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Q18">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="S18">
         <v>1.18</v>
@@ -3267,7 +3267,7 @@
         <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W18">
         <v>1.22</v>
@@ -3291,7 +3291,7 @@
         <v>1.94</v>
       </c>
       <c r="AD18">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AE18">
         <v>1.33</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AK18">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3572,22 +3572,22 @@
         <v>1.55</v>
       </c>
       <c r="O20">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="P20">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="Q20">
         <v>1.97</v>
       </c>
       <c r="R20">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="S20">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="T20">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="U20">
         <v>2.6</v>
@@ -3596,37 +3596,37 @@
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="X20">
         <v>1.02</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.92</v>
+        <v>3.81</v>
       </c>
       <c r="AA20">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AB20">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="AC20">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AD20">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE20">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF20">
+        <v>1.85</v>
+      </c>
+      <c r="AG20">
         <v>1.83</v>
-      </c>
-      <c r="AG20">
-        <v>1.85</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.15</v>
       </c>
       <c r="AK20">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -4061,13 +4061,13 @@
         <v>1.57</v>
       </c>
       <c r="O23">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P23">
-        <v>5.73</v>
+        <v>5.2</v>
       </c>
       <c r="Q23">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R23">
         <v>2.1</v>
@@ -4103,10 +4103,10 @@
         <v>1.69</v>
       </c>
       <c r="AC23">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD23">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE23">
         <v>1.03</v>
@@ -4115,7 +4115,7 @@
         <v>2.1</v>
       </c>
       <c r="AG23">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -674,10 +674,10 @@
         <v>4.2</v>
       </c>
       <c r="AA2">
-        <v>2.04</v>
+        <v>1.73</v>
       </c>
       <c r="AB2">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AC2">
         <v>2.74</v>
@@ -1613,25 +1613,25 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="Q8">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="R8">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="S8">
         <v>1.28</v>
       </c>
       <c r="T8">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="U8">
         <v>2.54</v>
@@ -1649,7 +1649,7 @@
         <v>1.19</v>
       </c>
       <c r="Z8">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="AA8">
         <v>1.59</v>
@@ -1670,7 +1670,7 @@
         <v>1.47</v>
       </c>
       <c r="AG8">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1993,10 +1993,10 @@
         <v>1.06</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2114,22 +2114,22 @@
         <v>3</v>
       </c>
       <c r="R11">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S11">
         <v>1.37</v>
       </c>
       <c r="T11">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="U11">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="V11">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
         <v>1.04</v>
@@ -2141,10 +2141,10 @@
         <v>3.5</v>
       </c>
       <c r="AA11">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="AB11">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
         <v>3.25</v>
@@ -2156,10 +2156,10 @@
         <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG11">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="U12">
         <v>2.68</v>
@@ -2292,7 +2292,7 @@
         <v>1.44</v>
       </c>
       <c r="W12">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2307,7 +2307,7 @@
         <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC12">
         <v>2.9</v>
@@ -2316,10 +2316,10 @@
         <v>1.4</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF12">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
         <v>1.73</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AK12">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="O13">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P13">
         <v>3</v>
@@ -2440,7 +2440,7 @@
         <v>2.9</v>
       </c>
       <c r="R13">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2464,7 +2464,7 @@
         <v>1.38</v>
       </c>
       <c r="Z13">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="AA13">
         <v>2.1</v>
@@ -2609,7 +2609,7 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U14">
         <v>2.63</v>
@@ -2627,13 +2627,13 @@
         <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>3.78</v>
+        <v>4.2</v>
       </c>
       <c r="AA14">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AB14">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC14">
         <v>2.88</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AK14">
         <v>1.5</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.43</v>
+        <v>2.63</v>
       </c>
       <c r="O15">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="P15">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="Q15">
-        <v>3.36</v>
+        <v>3.1</v>
       </c>
       <c r="R15">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="S15">
         <v>1.21</v>
@@ -2793,25 +2793,25 @@
         <v>6</v>
       </c>
       <c r="AA15">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AB15">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AC15">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="AD15">
         <v>1.65</v>
       </c>
       <c r="AE15">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AF15">
         <v>1.4</v>
       </c>
       <c r="AG15">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AK15">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P16">
-        <v>3.9</v>
+        <v>2.4</v>
       </c>
       <c r="Q16">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S16">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T16">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U16">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V16">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W16">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="X16">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y16">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z16">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="AA16">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AB16">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="AC16">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD16">
         <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF16">
         <v>1.62</v>
       </c>
       <c r="AG16">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AK16">
-        <v>2</v>
+        <v>1.44</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.8</v>
+        <v>1.63</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P17">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="Q17">
-        <v>3.2</v>
+        <v>2.11</v>
       </c>
       <c r="R17">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="S17">
         <v>1.3</v>
       </c>
       <c r="T17">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="U17">
-        <v>2.68</v>
+        <v>2.4</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y17">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z17">
-        <v>3.58</v>
+        <v>4.33</v>
       </c>
       <c r="AA17">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="AB17">
         <v>2.05</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF17">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG17">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK17">
-        <v>1.36</v>
+        <v>2.1</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -4719,34 +4719,34 @@
         <v>5.12</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T27">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="U27">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V27">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W27">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y27">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Z27">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA27">
         <v>1.65</v>
@@ -4755,19 +4755,19 @@
         <v>2.2</v>
       </c>
       <c r="AC27">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD27">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE27">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF27">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
@@ -4780,10 +4780,10 @@
         </is>
       </c>
       <c r="AJ27">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK27">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL27">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -807,22 +807,22 @@
         <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="U3">
         <v>2.89</v>
       </c>
       <c r="V3">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -840,7 +840,7 @@
         <v>2</v>
       </c>
       <c r="AB3">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC3">
         <v>3.5</v>
@@ -852,10 +852,10 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AG3">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="O4">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="P4">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AB4">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1785,7 +1785,7 @@
         <v>2.37</v>
       </c>
       <c r="Q9">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="R9">
         <v>2.25</v>
@@ -1812,10 +1812,10 @@
         <v>1.17</v>
       </c>
       <c r="Z9">
-        <v>4.32</v>
+        <v>4.36</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="AB9">
         <v>2.04</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>3.91</v>
+        <v>4.2</v>
       </c>
       <c r="O19">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="P19">
-        <v>1.68</v>
+        <v>1.59</v>
       </c>
       <c r="Q19">
         <v>3.8</v>
       </c>
       <c r="R19">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3439,10 +3439,10 @@
         <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AA19">
         <v>1.45</v>
@@ -3463,7 +3463,7 @@
         <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AK19">
         <v>1.22</v>
@@ -3732,25 +3732,25 @@
         </is>
       </c>
       <c r="N21">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="O21">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P21">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q21">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R21">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="S21">
         <v>1.29</v>
       </c>
       <c r="T21">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="U21">
         <v>2.39</v>
@@ -3762,19 +3762,19 @@
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
         <v>1.22</v>
       </c>
       <c r="Z21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB21">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC21">
         <v>2.66</v>
@@ -3783,10 +3783,10 @@
         <v>1.37</v>
       </c>
       <c r="AE21">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AK21">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3895,22 +3895,22 @@
         </is>
       </c>
       <c r="N22">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O22">
         <v>3.55</v>
       </c>
       <c r="P22">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q22">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="R22">
         <v>2.4</v>
       </c>
       <c r="S22">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="T22">
         <v>3.75</v>
@@ -3919,7 +3919,7 @@
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="W22">
         <v>1.14</v>
@@ -3928,31 +3928,31 @@
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z22">
-        <v>4.93</v>
+        <v>4.96</v>
       </c>
       <c r="AA22">
+        <v>1.42</v>
+      </c>
+      <c r="AB22">
+        <v>2.46</v>
+      </c>
+      <c r="AC22">
+        <v>2.24</v>
+      </c>
+      <c r="AD22">
+        <v>1.61</v>
+      </c>
+      <c r="AE22">
+        <v>1.23</v>
+      </c>
+      <c r="AF22">
         <v>1.44</v>
       </c>
-      <c r="AB22">
-        <v>2.45</v>
-      </c>
-      <c r="AC22">
-        <v>2.25</v>
-      </c>
-      <c r="AD22">
-        <v>1.59</v>
-      </c>
-      <c r="AE22">
-        <v>1.22</v>
-      </c>
-      <c r="AF22">
-        <v>1.5</v>
-      </c>
       <c r="AG22">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
@@ -3965,10 +3965,10 @@
         </is>
       </c>
       <c r="AJ22">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4242,10 +4242,10 @@
         <v>4.3</v>
       </c>
       <c r="U24">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="V24">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W24">
         <v>1.2</v>
@@ -4263,13 +4263,13 @@
         <v>1.36</v>
       </c>
       <c r="AB24">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AC24">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="AD24">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AE24">
         <v>1.25</v>
@@ -4278,7 +4278,7 @@
         <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.02</v>
       </c>
       <c r="AK24">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AL24">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -627,21 +627,21 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
-        <v>3.11</v>
+        <v>2.84</v>
       </c>
       <c r="O2">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P2">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q2">
         <v>3.7</v>
@@ -671,7 +671,7 @@
         <v>1.36</v>
       </c>
       <c r="Z2">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA2">
         <v>1.73</v>
@@ -701,11 +701,11 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["85"]</t>
         </is>
       </c>
       <c r="AJ2">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
         <v>1.3</v>
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>21</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,42 +787,42 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
-        <v>2.24</v>
+        <v>2.75</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q3">
-        <v>2.75</v>
+        <v>3.54</v>
       </c>
       <c r="R3">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
       <c r="U3">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="V3">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -852,14 +852,14 @@
         <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG3">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["69"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -868,37 +868,37 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="AK3">
-        <v>1.62</v>
+        <v>1.32</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.5</v>
+        <v>1.63</v>
       </c>
       <c r="O16">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P16">
+        <v>4</v>
+      </c>
+      <c r="Q16">
+        <v>2.11</v>
+      </c>
+      <c r="R16">
+        <v>2.22</v>
+      </c>
+      <c r="S16">
+        <v>1.3</v>
+      </c>
+      <c r="T16">
+        <v>3.3</v>
+      </c>
+      <c r="U16">
         <v>2.4</v>
       </c>
-      <c r="Q16">
-        <v>3</v>
-      </c>
-      <c r="R16">
-        <v>2.12</v>
-      </c>
-      <c r="S16">
-        <v>1.33</v>
-      </c>
-      <c r="T16">
-        <v>3</v>
-      </c>
-      <c r="U16">
+      <c r="V16">
+        <v>1.44</v>
+      </c>
+      <c r="W16">
+        <v>1.12</v>
+      </c>
+      <c r="X16">
+        <v>1.02</v>
+      </c>
+      <c r="Y16">
+        <v>1.22</v>
+      </c>
+      <c r="Z16">
+        <v>4.33</v>
+      </c>
+      <c r="AA16">
+        <v>1.72</v>
+      </c>
+      <c r="AB16">
+        <v>2.05</v>
+      </c>
+      <c r="AC16">
         <v>2.7</v>
       </c>
-      <c r="V16">
-        <v>1.45</v>
-      </c>
-      <c r="W16">
-        <v>1.06</v>
-      </c>
-      <c r="X16">
-        <v>1.04</v>
-      </c>
-      <c r="Y16">
-        <v>1.21</v>
-      </c>
-      <c r="Z16">
-        <v>3.58</v>
-      </c>
-      <c r="AA16">
-        <v>1.76</v>
-      </c>
-      <c r="AB16">
-        <v>1.95</v>
-      </c>
-      <c r="AC16">
-        <v>2.88</v>
-      </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF16">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AG16">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AK16">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.63</v>
+        <v>2.5</v>
       </c>
       <c r="O17">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P17">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="Q17">
-        <v>2.11</v>
+        <v>3</v>
       </c>
       <c r="R17">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="S17">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="T17">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="U17">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="V17">
+        <v>1.45</v>
+      </c>
+      <c r="W17">
+        <v>1.06</v>
+      </c>
+      <c r="X17">
+        <v>1.04</v>
+      </c>
+      <c r="Y17">
+        <v>1.21</v>
+      </c>
+      <c r="Z17">
+        <v>3.58</v>
+      </c>
+      <c r="AA17">
+        <v>1.76</v>
+      </c>
+      <c r="AB17">
+        <v>1.95</v>
+      </c>
+      <c r="AC17">
+        <v>2.88</v>
+      </c>
+      <c r="AD17">
+        <v>1.36</v>
+      </c>
+      <c r="AE17">
+        <v>1.13</v>
+      </c>
+      <c r="AF17">
+        <v>1.62</v>
+      </c>
+      <c r="AG17">
+        <v>2.12</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
+        <v>1.25</v>
+      </c>
+      <c r="AK17">
         <v>1.44</v>
-      </c>
-      <c r="W17">
-        <v>1.12</v>
-      </c>
-      <c r="X17">
-        <v>1.02</v>
-      </c>
-      <c r="Y17">
-        <v>1.22</v>
-      </c>
-      <c r="Z17">
-        <v>4.33</v>
-      </c>
-      <c r="AA17">
-        <v>1.72</v>
-      </c>
-      <c r="AB17">
-        <v>2.05</v>
-      </c>
-      <c r="AC17">
-        <v>2.7</v>
-      </c>
-      <c r="AD17">
-        <v>1.38</v>
-      </c>
-      <c r="AE17">
-        <v>1.17</v>
-      </c>
-      <c r="AF17">
-        <v>1.67</v>
-      </c>
-      <c r="AG17">
-        <v>2.15</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.11</v>
-      </c>
-      <c r="AK17">
-        <v>2.1</v>
       </c>
       <c r="AL17">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -967,7 +967,7 @@
         <v>3.95</v>
       </c>
       <c r="P4">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1000,10 +1000,10 @@
         <v>0</v>
       </c>
       <c r="AA4">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AB4">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC4">
         <v>0</v>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "72"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1101,54 +1101,54 @@
         </is>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P5">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="Q5">
-        <v>3.58</v>
+        <v>3.37</v>
       </c>
       <c r="R5">
         <v>2.05</v>
       </c>
       <c r="S5">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T5">
-        <v>2.99</v>
+        <v>2.55</v>
       </c>
       <c r="U5">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="W5">
         <v>1.06</v>
@@ -1157,74 +1157,74 @@
         <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z5">
         <v>4.33</v>
       </c>
       <c r="AA5">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AB5">
         <v>2.1</v>
       </c>
       <c r="AC5">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="AD5">
+        <v>1.45</v>
+      </c>
+      <c r="AE5">
+        <v>1.12</v>
+      </c>
+      <c r="AF5">
+        <v>1.53</v>
+      </c>
+      <c r="AG5">
+        <v>2.27</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>["67"]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>["39", "83", "90+2"]</t>
+        </is>
+      </c>
+      <c r="AJ5">
         <v>1.43</v>
       </c>
-      <c r="AE5">
-        <v>1.11</v>
-      </c>
-      <c r="AF5">
-        <v>1.57</v>
-      </c>
-      <c r="AG5">
-        <v>2.3</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ5">
-        <v>1.23</v>
-      </c>
       <c r="AK5">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1293,55 +1293,55 @@
         <v>4.5</v>
       </c>
       <c r="P6">
-        <v>5.7</v>
+        <v>6.05</v>
       </c>
       <c r="Q6">
         <v>1.91</v>
       </c>
       <c r="R6">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="S6">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="W6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="Z6">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA6">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.4</v>
+        <v>2.11</v>
       </c>
       <c r="AC6">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="AE6">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AG6">
         <v>2.05</v>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
         <v>2.4</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="O8">
         <v>3.4</v>
       </c>
       <c r="P8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="Q8">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="R8">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="S8">
         <v>1.28</v>
@@ -1634,10 +1634,10 @@
         <v>2.39</v>
       </c>
       <c r="U8">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="V8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
         <v>1.11</v>
@@ -1646,31 +1646,31 @@
         <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z8">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="AA8">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="AB8">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC8">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD8">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AF8">
         <v>1.47</v>
       </c>
       <c r="AG8">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>1.09</v>
       </c>
       <c r="AK8">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1782,55 +1782,55 @@
         <v>3.3</v>
       </c>
       <c r="P9">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Q9">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="R9">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S9">
         <v>1.29</v>
       </c>
       <c r="T9">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="U9">
         <v>2.38</v>
       </c>
       <c r="V9">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>4.36</v>
+        <v>4.24</v>
       </c>
       <c r="AA9">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="AB9">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC9">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AD9">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AG9">
         <v>2.25</v>
@@ -1948,22 +1948,22 @@
         <v>4.5</v>
       </c>
       <c r="Q10">
-        <v>2.45</v>
+        <v>2.39</v>
       </c>
       <c r="R10">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="S10">
         <v>1.44</v>
       </c>
       <c r="T10">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="U10">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="V10">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="W10">
         <v>1.03</v>
@@ -1972,22 +1972,22 @@
         <v>1.02</v>
       </c>
       <c r="Y10">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z10">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="AA10">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AB10">
         <v>1.57</v>
       </c>
       <c r="AC10">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD10">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE10">
         <v>1.06</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="O11">
         <v>3.3</v>
       </c>
       <c r="P11">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R11">
         <v>2.01</v>
       </c>
       <c r="S11">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="U11">
         <v>2.72</v>
@@ -2132,34 +2132,34 @@
         <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.29</v>
       </c>
       <c r="Z11">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA11">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AC11">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AD11">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AE11">
         <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG11">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AK11">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2268,28 +2268,28 @@
         <v>1.35</v>
       </c>
       <c r="O12">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="P12">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q12">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S12">
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.24</v>
+        <v>3.33</v>
       </c>
       <c r="U12">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="V12">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W12">
         <v>1.07</v>
@@ -2298,47 +2298,47 @@
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z12">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AA12">
         <v>1.75</v>
       </c>
       <c r="AB12">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="AD12">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE12">
+        <v>1.13</v>
+      </c>
+      <c r="AF12">
+        <v>2.07</v>
+      </c>
+      <c r="AG12">
+        <v>1.66</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ12">
         <v>1.14</v>
       </c>
-      <c r="AF12">
-        <v>2.05</v>
-      </c>
-      <c r="AG12">
-        <v>1.73</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12">
-        <v>1.06</v>
-      </c>
       <c r="AK12">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O13">
         <v>3.1</v>
@@ -2437,10 +2437,10 @@
         <v>3</v>
       </c>
       <c r="Q13">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="R13">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="S13">
         <v>1.4</v>
@@ -2461,16 +2461,16 @@
         <v>1.05</v>
       </c>
       <c r="Y13">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Z13">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="AA13">
         <v>2.1</v>
       </c>
       <c r="AB13">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AC13">
         <v>3.7</v>
@@ -2501,7 +2501,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2609,28 +2609,28 @@
         <v>1.3</v>
       </c>
       <c r="T14">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U14">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="V14">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="W14">
         <v>1.1</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y14">
         <v>1.22</v>
       </c>
       <c r="Z14">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA14">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AB14">
         <v>2</v>
@@ -2642,13 +2642,13 @@
         <v>1.4</v>
       </c>
       <c r="AE14">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AF14">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AK14">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,58 +2754,58 @@
         </is>
       </c>
       <c r="N15">
-        <v>2.63</v>
+        <v>2.43</v>
       </c>
       <c r="O15">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="P15">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q15">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R15">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S15">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="T15">
-        <v>3.58</v>
+        <v>3.72</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V15">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W15">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="X15">
         <v>1.02</v>
       </c>
       <c r="Y15">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="AA15">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="AB15">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="AC15">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AD15">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AE15">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AF15">
         <v>1.4</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AK15">
         <v>1.44</v>
@@ -2917,19 +2917,19 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="O16">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="Q16">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="R16">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.3</v>
@@ -2953,28 +2953,28 @@
         <v>1.22</v>
       </c>
       <c r="Z16">
-        <v>4.33</v>
+        <v>4.22</v>
       </c>
       <c r="AA16">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AB16">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AC16">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AD16">
         <v>1.38</v>
       </c>
       <c r="AE16">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG16">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AK16">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3080,19 +3080,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
         <v>3.25</v>
       </c>
       <c r="P17">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q17">
         <v>3</v>
       </c>
       <c r="R17">
-        <v>2.12</v>
+        <v>2.15</v>
       </c>
       <c r="S17">
         <v>1.33</v>
@@ -3101,10 +3101,10 @@
         <v>3</v>
       </c>
       <c r="U17">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="V17">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W17">
         <v>1.06</v>
@@ -3119,13 +3119,13 @@
         <v>3.58</v>
       </c>
       <c r="AA17">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AB17">
         <v>1.95</v>
       </c>
       <c r="AC17">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="AD17">
         <v>1.36</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="O18">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="P18">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="Q18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R18">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="S18">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T18">
-        <v>3.92</v>
+        <v>4.05</v>
       </c>
       <c r="U18">
         <v>1.95</v>
       </c>
       <c r="V18">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="W18">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="X18">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Z18">
         <v>6.5</v>
@@ -3288,7 +3288,7 @@
         <v>3.1</v>
       </c>
       <c r="AC18">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="AD18">
         <v>1.87</v>
@@ -3300,7 +3300,7 @@
         <v>1.36</v>
       </c>
       <c r="AG18">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AK18">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3406,19 +3406,19 @@
         </is>
       </c>
       <c r="N19">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O19">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="P19">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="Q19">
         <v>3.8</v>
       </c>
       <c r="R19">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S19">
         <v>1.22</v>
@@ -3433,7 +3433,7 @@
         <v>1.5</v>
       </c>
       <c r="W19">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X19">
         <v>1.02</v>
@@ -3442,10 +3442,10 @@
         <v>1.12</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AA19">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AB19">
         <v>2.35</v>
@@ -3463,7 +3463,7 @@
         <v>1.44</v>
       </c>
       <c r="AG19">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.95</v>
       </c>
       <c r="AK19">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="O20">
         <v>4</v>
@@ -3578,16 +3578,16 @@
         <v>5.25</v>
       </c>
       <c r="Q20">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="R20">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="S20">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="T20">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="U20">
         <v>2.6</v>
@@ -3596,25 +3596,25 @@
         <v>1.44</v>
       </c>
       <c r="W20">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X20">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y20">
         <v>1.22</v>
       </c>
       <c r="Z20">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="AA20">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AB20">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>2.83</v>
+        <v>2.74</v>
       </c>
       <c r="AD20">
         <v>1.33</v>
@@ -3623,7 +3623,7 @@
         <v>1.1</v>
       </c>
       <c r="AF20">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
         <v>1.83</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AK20">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,19 +3732,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>2.85</v>
+        <v>2.39</v>
       </c>
       <c r="O21">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="P21">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="Q21">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R21">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="S21">
         <v>1.29</v>
@@ -3762,7 +3762,7 @@
         <v>1.07</v>
       </c>
       <c r="X21">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y21">
         <v>1.22</v>
@@ -3771,22 +3771,22 @@
         <v>4.1</v>
       </c>
       <c r="AA21">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AB21">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="AC21">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AD21">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AE21">
         <v>1.11</v>
       </c>
       <c r="AF21">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AG21">
         <v>2.25</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AK21">
         <v>1.44</v>
@@ -3898,16 +3898,16 @@
         <v>3.1</v>
       </c>
       <c r="O22">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="P22">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="Q22">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="R22">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="S22">
         <v>1.19</v>
@@ -3919,28 +3919,28 @@
         <v>2.1</v>
       </c>
       <c r="V22">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W22">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X22">
         <v>1.02</v>
       </c>
       <c r="Y22">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z22">
-        <v>4.96</v>
+        <v>5.4</v>
       </c>
       <c r="AA22">
         <v>1.42</v>
       </c>
       <c r="AB22">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="AC22">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AD22">
         <v>1.61</v>
@@ -3968,7 +3968,7 @@
         <v>1.18</v>
       </c>
       <c r="AK22">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -4058,13 +4058,13 @@
         </is>
       </c>
       <c r="N23">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="O23">
         <v>3.55</v>
       </c>
       <c r="P23">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q23">
         <v>2.16</v>
@@ -4073,16 +4073,16 @@
         <v>2.1</v>
       </c>
       <c r="S23">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T23">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="U23">
-        <v>3.02</v>
+        <v>3.09</v>
       </c>
       <c r="V23">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W23">
         <v>1.05</v>
@@ -4091,31 +4091,31 @@
         <v>1.01</v>
       </c>
       <c r="Y23">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z23">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="AA23">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AB23">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AC23">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AD23">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE23">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF23">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG23">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>1.72</v>
       </c>
       <c r="W24">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="X24">
         <v>1.01</v>
@@ -4269,16 +4269,16 @@
         <v>1.99</v>
       </c>
       <c r="AD24">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AE24">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AF24">
         <v>1.95</v>
       </c>
       <c r="AG24">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>1.02</v>
       </c>
       <c r="AK24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL24">
         <v>0</v>
@@ -4423,10 +4423,10 @@
         <v>0</v>
       </c>
       <c r="AA25">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AB25">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC25">
         <v>0</v>

--- a/jogos_2026-09-25.xlsx
+++ b/jogos_2026-09-25.xlsx
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["6", "43"]</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -1366,28 +1366,28 @@
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>20</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1590,26 +1590,26 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8">
         <v>0</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["80"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "25", "58"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1768,11 +1768,11 @@
         <v>0</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+5"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["58"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Stenhousemuir</t>
         </is>
       </c>
       <c r="G10">
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -1935,68 +1935,68 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
-        <v>1.76</v>
+        <v>2.2</v>
       </c>
       <c r="O10">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="P10">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>2.39</v>
+        <v>3</v>
       </c>
       <c r="R10">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="S10">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T10">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="U10">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="V10">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X10">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y10">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="Z10">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="AA10">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AB10">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="AC10">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD10">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE10">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF10">
-        <v>2.15</v>
+        <v>1.84</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2005,41 +2005,41 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["20"]</t>
         </is>
       </c>
       <c r="AJ10">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK10">
-        <v>1.86</v>
+        <v>1.52</v>
       </c>
       <c r="AL10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2070,139 +2070,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Inverness CT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
         <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
-        <v>2.6</v>
+        <v>1.35</v>
       </c>
       <c r="O11">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="P11">
-        <v>2.45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="Q11">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="R11">
-        <v>2.01</v>
+        <v>2.5</v>
       </c>
       <c r="S11">
         <v>1.33</v>
       </c>
       <c r="T11">
-        <v>3.06</v>
+        <v>3.33</v>
       </c>
       <c r="U11">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="V11">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z11">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA11">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AB11">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="AC11">
-        <v>3.08</v>
+        <v>2.74</v>
       </c>
       <c r="AD11">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>1.67</v>
+        <v>2.07</v>
       </c>
       <c r="AG11">
-        <v>2.05</v>
+        <v>1.66</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
+          <t>["26", "66"]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ11">
-        <v>1.44</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>1.4</v>
+        <v>2.98</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2233,19 +2233,19 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Inverness CT</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G12">
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,72 +2257,72 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
-        <v>1.35</v>
+        <v>2.6</v>
       </c>
       <c r="O12">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="P12">
-        <v>9.300000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="R12">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="S12">
         <v>1.33</v>
       </c>
       <c r="T12">
-        <v>3.33</v>
+        <v>3.06</v>
       </c>
       <c r="U12">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="W12">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z12">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AA12">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC12">
-        <v>2.74</v>
+        <v>3.08</v>
       </c>
       <c r="AD12">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AE12">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>2.07</v>
+        <v>1.67</v>
       </c>
       <c r="AG12">
-        <v>1.66</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2331,41 +2331,41 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["46", "60"]</t>
         </is>
       </c>
       <c r="AJ12">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AK12">
-        <v>2.98</v>
+        <v>1.4</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2396,22 +2396,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stenhousemuir</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,115 +2420,115 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
+        <v>1.76</v>
+      </c>
+      <c r="O13">
+        <v>3.2</v>
+      </c>
+      <c r="P13">
+        <v>4.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.39</v>
+      </c>
+      <c r="R13">
+        <v>1.95</v>
+      </c>
+      <c r="S13">
+        <v>1.44</v>
+      </c>
+      <c r="T13">
+        <v>2.51</v>
+      </c>
+      <c r="U13">
+        <v>3.3</v>
+      </c>
+      <c r="V13">
+        <v>1.29</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.02</v>
+      </c>
+      <c r="Y13">
+        <v>1.36</v>
+      </c>
+      <c r="Z13">
+        <v>2.7</v>
+      </c>
+      <c r="AA13">
         <v>2.2</v>
       </c>
-      <c r="O13">
-        <v>3.1</v>
-      </c>
-      <c r="P13">
+      <c r="AB13">
+        <v>1.57</v>
+      </c>
+      <c r="AC13">
+        <v>4.1</v>
+      </c>
+      <c r="AD13">
+        <v>1.23</v>
+      </c>
+      <c r="AE13">
+        <v>1.06</v>
+      </c>
+      <c r="AF13">
+        <v>2.15</v>
+      </c>
+      <c r="AG13">
+        <v>1.67</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>["11", "44"]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>["74"]</t>
+        </is>
+      </c>
+      <c r="AJ13">
+        <v>1.3</v>
+      </c>
+      <c r="AK13">
+        <v>1.86</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>2</v>
+      </c>
+      <c r="AN13">
         <v>3</v>
       </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
-      <c r="R13">
-        <v>1.96</v>
-      </c>
-      <c r="S13">
-        <v>1.4</v>
-      </c>
-      <c r="T13">
-        <v>2.75</v>
-      </c>
-      <c r="U13">
-        <v>2.99</v>
-      </c>
-      <c r="V13">
-        <v>1.34</v>
-      </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.05</v>
-      </c>
-      <c r="Y13">
-        <v>1.39</v>
-      </c>
-      <c r="Z13">
-        <v>3</v>
-      </c>
-      <c r="AA13">
-        <v>2.1</v>
-      </c>
-      <c r="AB13">
-        <v>1.63</v>
-      </c>
-      <c r="AC13">
-        <v>3.7</v>
-      </c>
-      <c r="AD13">
-        <v>1.2</v>
-      </c>
-      <c r="AE13">
-        <v>1.04</v>
-      </c>
-      <c r="AF13">
-        <v>1.84</v>
-      </c>
-      <c r="AG13">
-        <v>1.85</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ13">
-        <v>1.33</v>
-      </c>
-      <c r="AK13">
-        <v>1.52</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>-1</v>
-      </c>
-      <c r="AN13">
-        <v>-1</v>
-      </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -2580,14 +2580,14 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14">
         <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -2670,28 +2670,28 @@
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN14">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ14">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
@@ -2731,26 +2731,26 @@
         </is>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I15">
         <v>0</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["30", "56", "60"]</t>
         </is>
       </c>
       <c r="AJ15">
@@ -2833,28 +2833,28 @@
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ15">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
@@ -2894,26 +2894,26 @@
         </is>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16">
@@ -2978,12 +2978,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45", "67"]</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["43"]</t>
         </is>
       </c>
       <c r="AJ16">
@@ -2996,28 +2996,28 @@
         <v>0</v>
       </c>
       <c r="AM16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
@@ -3057,26 +3057,26 @@
         </is>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["9", "67", "77"]</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["38", "51", "55"]</t>
         </is>
       </c>
       <c r="AJ17">
@@ -3159,28 +3159,28 @@
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
@@ -3220,26 +3220,26 @@
         </is>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N18">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["22", "58", "90+1"]</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["10", "90"]</t>
         </is>
       </c>
       <c r="AJ18">
@@ -3322,28 +3322,28 @@
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP18">
-        <v>-1</v>
+        <v>19</v>
       </c>
       <c r="AQ18">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR18">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS18">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="AT18">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
